--- a/python/naver_movie_crawler/crawling/navermovie.xlsx
+++ b/python/naver_movie_crawler/crawling/navermovie.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20372"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20373"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zz238\TIL\python\naver_movie_crawler\crawling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC1A02A-1B5D-43D9-8211-BD211EA05616}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6761C36C-1426-40D4-8B5B-5049842E2BE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3436,9 +3436,6 @@
     <t xml:space="preserve"> 7.03</t>
   </si>
   <si>
-    <t>#살아있다</t>
-  </si>
-  <si>
     <t>189537</t>
   </si>
   <si>
@@ -3473,9 +3470,6 @@
   </si>
   <si>
     <t xml:space="preserve"> 8.57</t>
-  </si>
-  <si>
-    <t>#아이엠히어</t>
   </si>
   <si>
     <t>189457</t>
@@ -7743,6 +7737,14 @@
   </si>
   <si>
     <t>2020.06.18 개봉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이엠히어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>살아있다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8119,7 +8121,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -9704,25 +9706,25 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="B51" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="C51" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="D51" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="E51" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="F51" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="G51" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="H51" t="s">
         <v>969</v>
@@ -9736,10 +9738,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="B52" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="C52" t="s">
         <v>756</v>
@@ -9748,19 +9750,19 @@
         <v>526</v>
       </c>
       <c r="E52" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="F52" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="G52" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="H52" t="s">
         <v>85</v>
       </c>
       <c r="I52" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="J52">
         <v>19000</v>
@@ -9768,28 +9770,28 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="B53" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="C53" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="D53" t="s">
         <v>106</v>
       </c>
       <c r="E53" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="F53" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="G53" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="H53" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="I53" t="s">
         <v>385</v>
@@ -9800,28 +9802,28 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="B54" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="C54" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="D54" t="s">
         <v>916</v>
       </c>
       <c r="E54" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="F54" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="G54" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="H54" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="I54" t="s">
         <v>950</v>
@@ -9832,28 +9834,28 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="B55" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="C55" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D55" t="s">
         <v>65</v>
       </c>
       <c r="E55" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="F55" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="G55" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="H55" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="I55" t="s">
         <v>836</v>
@@ -9864,10 +9866,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="B56" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="C56" t="s">
         <v>29</v>
@@ -9876,16 +9878,16 @@
         <v>106</v>
       </c>
       <c r="E56" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="F56" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="G56" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="H56" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="I56" t="s">
         <v>179</v>
@@ -9896,25 +9898,25 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="B57" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="C57" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="D57" t="s">
         <v>1032</v>
       </c>
       <c r="E57" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="F57" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="G57" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="H57" t="s">
         <v>937</v>
@@ -9928,25 +9930,25 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="B58" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="C58" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="D58" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="E58" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="F58" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="G58" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="H58" t="s">
         <v>618</v>
@@ -9960,10 +9962,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="B59" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="C59" t="s">
         <v>1071</v>
@@ -9972,16 +9974,16 @@
         <v>160</v>
       </c>
       <c r="E59" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="F59" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="G59" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="H59" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="I59" t="s">
         <v>919</v>
@@ -9992,28 +9994,28 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="B60" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="C60" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="D60" t="s">
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="F60" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="G60" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="H60" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="I60" t="s">
         <v>700</v>
@@ -10024,28 +10026,28 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="B61" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="C61" t="s">
         <v>472</v>
       </c>
       <c r="D61" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="E61" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="F61" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="G61" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="H61" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="I61" t="s">
         <v>61</v>
@@ -10056,25 +10058,25 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="B62" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="C62" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="D62" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="E62" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="F62" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="G62" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="H62" t="s">
         <v>42</v>
@@ -10088,25 +10090,25 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="B63" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="C63" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="D63" t="s">
         <v>302</v>
       </c>
       <c r="E63" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="F63" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="G63" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="H63" t="s">
         <v>599</v>
@@ -10120,25 +10122,25 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="B64" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="C64" t="s">
         <v>89</v>
       </c>
       <c r="D64" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="E64" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="F64" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="G64" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="H64" t="s">
         <v>366</v>
@@ -10152,10 +10154,10 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="B65" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="C65" t="s">
         <v>433</v>
@@ -10164,13 +10166,13 @@
         <v>106</v>
       </c>
       <c r="E65" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="F65" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="G65" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="H65" t="s">
         <v>69</v>
@@ -10184,10 +10186,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="B66" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="C66" t="s">
         <v>782</v>
@@ -10196,19 +10198,19 @@
         <v>106</v>
       </c>
       <c r="E66" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="F66" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="G66" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="H66" t="s">
         <v>611</v>
       </c>
       <c r="I66" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="J66">
         <v>9000</v>
@@ -10216,25 +10218,25 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="B67" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="C67" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="D67" t="s">
         <v>1107</v>
       </c>
       <c r="E67" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="F67" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="G67" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="H67" t="s">
         <v>443</v>
@@ -10248,10 +10250,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="B68" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="C68" t="s">
         <v>676</v>
@@ -10260,16 +10262,16 @@
         <v>56</v>
       </c>
       <c r="E68" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="F68" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="G68" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="H68" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="I68" t="s">
         <v>1035</v>
@@ -10280,25 +10282,25 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="B69" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="C69" t="s">
         <v>237</v>
       </c>
       <c r="D69" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="E69" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="F69" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="G69" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="H69" t="s">
         <v>501</v>
@@ -10312,25 +10314,25 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="B70" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="C70" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="D70" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="E70" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="F70" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="G70" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="H70" t="s">
         <v>771</v>
@@ -10344,28 +10346,28 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="B71" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="C71" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="D71" t="s">
         <v>56</v>
       </c>
       <c r="E71" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="F71" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="G71" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="H71" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="I71" t="s">
         <v>43</v>
@@ -10376,10 +10378,10 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="B72" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="C72" t="s">
         <v>790</v>
@@ -10388,13 +10390,13 @@
         <v>568</v>
       </c>
       <c r="E72" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="F72" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="G72" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="H72" t="s">
         <v>481</v>
@@ -10408,31 +10410,31 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="B73" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="C73" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="D73" t="s">
         <v>65</v>
       </c>
       <c r="E73" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="F73" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="G73" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="H73" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="I73" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="J73">
         <v>18000</v>
@@ -10440,25 +10442,25 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="B74" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="C74" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="D74" t="s">
         <v>424</v>
       </c>
       <c r="E74" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="F74" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="G74" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="H74" t="s">
         <v>716</v>
@@ -10472,25 +10474,25 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="B75" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="C75" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="D75" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="E75" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="F75" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="G75" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="H75" t="s">
         <v>366</v>
@@ -10504,10 +10506,10 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="B76" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="C76" t="s">
         <v>274</v>
@@ -10516,13 +10518,13 @@
         <v>65</v>
       </c>
       <c r="E76" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="F76" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="G76" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="H76" t="s">
         <v>925</v>
@@ -10536,28 +10538,28 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="B77" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="C77" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="D77" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="E77" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="F77" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="G77" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="H77" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="I77" t="s">
         <v>249</v>
@@ -10568,10 +10570,10 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="B78" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="C78" t="s">
         <v>1053</v>
@@ -10580,16 +10582,16 @@
         <v>230</v>
       </c>
       <c r="E78" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="F78" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="G78" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="H78" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="I78" t="s">
         <v>686</v>
@@ -10600,31 +10602,31 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="B79" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="C79" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="D79" t="s">
         <v>916</v>
       </c>
       <c r="E79" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="F79" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="G79" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="H79" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="I79" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="J79">
         <v>7000</v>
@@ -10632,28 +10634,28 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="B80" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="C80" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="D80" t="s">
         <v>526</v>
       </c>
       <c r="E80" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="F80" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="G80" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="H80" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="I80" t="s">
         <v>820</v>
@@ -10664,31 +10666,31 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="B81" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="C81" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
       </c>
       <c r="E81" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="F81" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="G81" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="H81" t="s">
         <v>194</v>
       </c>
       <c r="I81" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="J81">
         <v>6000</v>
@@ -10696,10 +10698,10 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="B82" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="C82" t="s">
         <v>190</v>
@@ -10708,13 +10710,13 @@
         <v>603</v>
       </c>
       <c r="E82" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="F82" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="G82" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="H82" t="s">
         <v>1049</v>
@@ -10728,28 +10730,28 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="B83" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="C83" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="D83" t="s">
         <v>603</v>
       </c>
       <c r="E83" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="F83" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="G83" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="H83" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="I83" t="s">
         <v>258</v>
@@ -10760,10 +10762,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="B84" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="C84" t="s">
         <v>37</v>
@@ -10772,19 +10774,19 @@
         <v>230</v>
       </c>
       <c r="E84" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="F84" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="G84" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="H84" t="s">
         <v>142</v>
       </c>
       <c r="I84" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="J84">
         <v>7000</v>
@@ -10792,10 +10794,10 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="B85" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="C85" t="s">
         <v>37</v>
@@ -10804,13 +10806,13 @@
         <v>817</v>
       </c>
       <c r="E85" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="F85" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="G85" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="H85" t="s">
         <v>156</v>
@@ -10824,28 +10826,28 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="B86" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C86" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="D86" t="s">
         <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="F86" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="G86" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="H86" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="I86" t="s">
         <v>187</v>
@@ -10856,10 +10858,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="B87" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="C87" t="s">
         <v>1108</v>
@@ -10868,16 +10870,16 @@
         <v>424</v>
       </c>
       <c r="E87" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="F87" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="G87" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="H87" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="I87" t="s">
         <v>321</v>
@@ -10888,28 +10890,28 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="B88" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="C88" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="D88" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="E88" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="F88" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="G88" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="H88" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="I88" t="s">
         <v>226</v>
@@ -10920,28 +10922,28 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="B89" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="C89" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="D89" t="s">
         <v>1107</v>
       </c>
       <c r="E89" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="F89" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="G89" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="H89" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="I89" t="s">
         <v>1035</v>
@@ -10952,25 +10954,25 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="B90" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="C90" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="D90" t="s">
         <v>106</v>
       </c>
       <c r="E90" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="F90" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="G90" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="H90" t="s">
         <v>618</v>
@@ -10984,25 +10986,25 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="B91" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="C91" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="D91" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E91" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="F91" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="G91" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="H91" t="s">
         <v>248</v>
@@ -11016,10 +11018,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="B92" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="C92" t="s">
         <v>782</v>
@@ -11028,16 +11030,16 @@
         <v>65</v>
       </c>
       <c r="E92" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="F92" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="G92" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="H92" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="I92" t="s">
         <v>157</v>
@@ -11048,25 +11050,25 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="B93" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="C93" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="D93" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="E93" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="F93" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="G93" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="H93" t="s">
         <v>999</v>
@@ -11080,28 +11082,28 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="B94" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="C94" t="s">
         <v>361</v>
       </c>
       <c r="D94" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="E94" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="F94" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="G94" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="H94" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="I94" t="s">
         <v>187</v>
@@ -11112,31 +11114,31 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="B95" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="C95" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="D95" t="s">
         <v>1015</v>
       </c>
       <c r="E95" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="F95" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="G95" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="H95" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="I95" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="J95">
         <v>18000</v>
@@ -11144,25 +11146,25 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="B96" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="C96" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="D96" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="E96" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="F96" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="G96" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H96" t="s">
         <v>248</v>
@@ -11176,28 +11178,28 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="B97" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="C97" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="D97" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="E97" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="F97" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G97" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="H97" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="I97" t="s">
         <v>700</v>
@@ -11208,25 +11210,25 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="B98" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="C98" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="D98" t="s">
         <v>65</v>
       </c>
       <c r="E98" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="F98" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="G98" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="H98" t="s">
         <v>489</v>
@@ -11240,31 +11242,31 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="B99" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="C99" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D99" t="s">
         <v>106</v>
       </c>
       <c r="E99" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="F99" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="G99" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="H99" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="I99" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="J99">
         <v>14000</v>
@@ -11272,28 +11274,28 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="B100" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="C100" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="D100" t="s">
         <v>106</v>
       </c>
       <c r="E100" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F100" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="G100" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="H100" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="I100" t="s">
         <v>739</v>
@@ -11304,10 +11306,10 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="B101" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="C101" t="s">
         <v>676</v>
@@ -11316,16 +11318,16 @@
         <v>603</v>
       </c>
       <c r="E101" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="F101" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="G101" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="H101" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="I101" t="s">
         <v>218</v>
@@ -11336,25 +11338,25 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="B102" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C102" t="s">
         <v>1572</v>
-      </c>
-      <c r="C102" t="s">
-        <v>1574</v>
       </c>
       <c r="D102" t="s">
         <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F102" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="G102" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="H102" t="s">
         <v>366</v>
@@ -11368,10 +11370,10 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="B103" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="C103" t="s">
         <v>790</v>
@@ -11380,16 +11382,16 @@
         <v>81</v>
       </c>
       <c r="E103" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="F103" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G103" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="H103" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="I103" t="s">
         <v>143</v>
@@ -11400,10 +11402,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="B104" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="C104" t="s">
         <v>809</v>
@@ -11412,16 +11414,16 @@
         <v>56</v>
       </c>
       <c r="E104" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="F104" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="G104" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="H104" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="I104" t="s">
         <v>86</v>
@@ -11432,28 +11434,28 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="B105" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="C105" t="s">
         <v>728</v>
       </c>
       <c r="D105" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="E105" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="F105" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="G105" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="H105" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="I105" t="s">
         <v>385</v>
@@ -11464,10 +11466,10 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B106" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C106" t="s">
         <v>569</v>
@@ -11476,16 +11478,16 @@
         <v>65</v>
       </c>
       <c r="E106" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="F106" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="G106" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="H106" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="I106" t="s">
         <v>328</v>
@@ -11496,25 +11498,25 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="B107" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="C107" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="D107" t="s">
         <v>817</v>
       </c>
       <c r="E107" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="F107" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="G107" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="H107" t="s">
         <v>399</v>
@@ -11528,10 +11530,10 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="B108" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="C108" t="s">
         <v>80</v>
@@ -11540,13 +11542,13 @@
         <v>547</v>
       </c>
       <c r="E108" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="F108" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="G108" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="H108" t="s">
         <v>16</v>
@@ -11560,10 +11562,10 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="B109" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="C109" t="s">
         <v>11</v>
@@ -11572,13 +11574,13 @@
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="F109" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="G109" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="H109" t="s">
         <v>278</v>
@@ -11592,28 +11594,28 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="B110" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="C110" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="D110" t="s">
         <v>230</v>
       </c>
       <c r="E110" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="F110" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="G110" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="H110" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="I110" t="s">
         <v>820</v>
@@ -11624,10 +11626,10 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="B111" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="C111" t="s">
         <v>448</v>
@@ -11636,16 +11638,16 @@
         <v>65</v>
       </c>
       <c r="E111" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="F111" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="G111" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="H111" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="I111" t="s">
         <v>249</v>
@@ -11656,25 +11658,25 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B112" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="C112" t="s">
         <v>676</v>
       </c>
       <c r="D112" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="E112" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="F112" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="G112" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="H112" t="s">
         <v>899</v>
@@ -11688,25 +11690,25 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="B113" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="C113" t="s">
         <v>37</v>
       </c>
       <c r="D113" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="E113" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="F113" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="G113" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="H113" t="s">
         <v>343</v>
@@ -11720,10 +11722,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="B114" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C114" t="s">
         <v>1016</v>
@@ -11732,13 +11734,13 @@
         <v>455</v>
       </c>
       <c r="E114" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="F114" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="G114" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="H114" t="s">
         <v>320</v>
@@ -11752,31 +11754,31 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B115" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="C115" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="D115" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="E115" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="F115" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="G115" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="H115" t="s">
         <v>278</v>
       </c>
       <c r="I115" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="J115">
         <v>7000</v>
@@ -11784,28 +11786,28 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B116" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="C116" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D116" t="s">
         <v>21</v>
       </c>
       <c r="E116" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="F116" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="G116" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="H116" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="I116" t="s">
         <v>94</v>
@@ -11816,28 +11818,28 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="B117" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C117" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="D117" t="s">
         <v>21</v>
       </c>
       <c r="E117" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="F117" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="G117" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="H117" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="I117" t="s">
         <v>1035</v>
@@ -11848,10 +11850,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="B118" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="C118" t="s">
         <v>676</v>
@@ -11860,19 +11862,19 @@
         <v>302</v>
       </c>
       <c r="E118" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="F118" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="G118" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="H118" t="s">
         <v>1074</v>
       </c>
       <c r="I118" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="J118">
         <v>10000</v>
@@ -11880,10 +11882,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="B119" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="C119" t="s">
         <v>853</v>
@@ -11892,13 +11894,13 @@
         <v>302</v>
       </c>
       <c r="E119" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="F119" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="G119" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="H119" t="s">
         <v>985</v>
@@ -11912,28 +11914,28 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B120" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="C120" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="D120" t="s">
         <v>65</v>
       </c>
       <c r="E120" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="F120" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="G120" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="H120" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="I120" t="s">
         <v>111</v>
@@ -11944,25 +11946,25 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="B121" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="C121" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="D121" t="s">
         <v>989</v>
       </c>
       <c r="E121" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="F121" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="G121" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="H121" t="s">
         <v>241</v>
@@ -11976,28 +11978,28 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="B122" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="C122" t="s">
         <v>782</v>
       </c>
       <c r="D122" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="E122" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="F122" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="G122" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="H122" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="I122" t="s">
         <v>976</v>
@@ -12008,10 +12010,10 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="B123" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="C123" t="s">
         <v>712</v>
@@ -12020,13 +12022,13 @@
         <v>72</v>
       </c>
       <c r="E123" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="F123" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G123" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="H123" t="s">
         <v>580</v>
@@ -12040,10 +12042,10 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="B124" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="C124" t="s">
         <v>37</v>
@@ -12052,19 +12054,19 @@
         <v>106</v>
       </c>
       <c r="E124" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="F124" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="G124" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="H124" t="s">
         <v>142</v>
       </c>
       <c r="I124" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="J124">
         <v>10000</v>
@@ -12072,10 +12074,10 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="B125" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="C125" t="s">
         <v>472</v>
@@ -12084,16 +12086,16 @@
         <v>65</v>
       </c>
       <c r="E125" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="F125" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="G125" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="H125" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I125" t="s">
         <v>572</v>
@@ -12104,28 +12106,28 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B126" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="C126" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D126" t="s">
         <v>65</v>
       </c>
       <c r="E126" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="F126" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G126" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="H126" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="I126" t="s">
         <v>820</v>
@@ -12136,10 +12138,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B127" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="C127" t="s">
         <v>64</v>
@@ -12148,13 +12150,13 @@
         <v>577</v>
       </c>
       <c r="E127" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="F127" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="G127" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="H127" t="s">
         <v>373</v>
@@ -12168,10 +12170,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="B128" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="C128" t="s">
         <v>370</v>
@@ -12180,13 +12182,13 @@
         <v>65</v>
       </c>
       <c r="E128" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F128" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G128" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="H128" t="s">
         <v>899</v>
@@ -12200,25 +12202,25 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B129" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="C129" t="s">
         <v>131</v>
       </c>
       <c r="D129" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="E129" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F129" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="G129" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H129" t="s">
         <v>786</v>
@@ -12232,25 +12234,25 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B130" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="C130" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="D130" t="s">
         <v>65</v>
       </c>
       <c r="E130" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="F130" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="G130" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="H130" t="s">
         <v>618</v>
@@ -12264,10 +12266,10 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B131" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C131" t="s">
         <v>676</v>
@@ -12276,16 +12278,16 @@
         <v>65</v>
       </c>
       <c r="E131" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F131" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="G131" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H131" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="I131" t="s">
         <v>1035</v>
@@ -12296,25 +12298,25 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B132" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C132" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D132" t="s">
         <v>455</v>
       </c>
       <c r="E132" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="F132" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="G132" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="H132" t="s">
         <v>985</v>
@@ -12328,10 +12330,10 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="B133" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="C133" t="s">
         <v>29</v>
@@ -12340,19 +12342,19 @@
         <v>106</v>
       </c>
       <c r="E133" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="F133" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="G133" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="H133" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="I133" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="J133">
         <v>10000</v>
@@ -12360,28 +12362,28 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B134" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="C134" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="D134" t="s">
         <v>65</v>
       </c>
       <c r="E134" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="F134" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="G134" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="H134" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="I134" t="s">
         <v>950</v>
@@ -12392,10 +12394,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B135" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="C135" t="s">
         <v>353</v>
@@ -12404,13 +12406,13 @@
         <v>485</v>
       </c>
       <c r="E135" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="F135" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="G135" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H135" t="s">
         <v>786</v>
@@ -12424,10 +12426,10 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B136" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="C136" t="s">
         <v>1078</v>
@@ -12436,13 +12438,13 @@
         <v>916</v>
       </c>
       <c r="E136" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="F136" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="G136" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="H136" t="s">
         <v>320</v>
@@ -12456,10 +12458,10 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B137" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="C137" t="s">
         <v>966</v>
@@ -12468,13 +12470,13 @@
         <v>21</v>
       </c>
       <c r="E137" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="F137" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="G137" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="H137" t="s">
         <v>76</v>
@@ -12488,31 +12490,31 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B138" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="C138" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="D138" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="E138" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F138" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="G138" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="H138" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="I138" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="J138">
         <v>15000</v>
@@ -12520,10 +12522,10 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="B139" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C139" t="s">
         <v>835</v>
@@ -12532,13 +12534,13 @@
         <v>65</v>
       </c>
       <c r="E139" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="F139" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="G139" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="H139" t="s">
         <v>327</v>
@@ -12552,10 +12554,10 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B140" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C140" t="s">
         <v>190</v>
@@ -12564,13 +12566,13 @@
         <v>302</v>
       </c>
       <c r="E140" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="F140" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="G140" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="H140" t="s">
         <v>320</v>
@@ -12584,10 +12586,10 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B141" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="C141" t="s">
         <v>1040</v>
@@ -12596,13 +12598,13 @@
         <v>748</v>
       </c>
       <c r="E141" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="F141" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="G141" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="H141" t="s">
         <v>414</v>
@@ -12616,25 +12618,25 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B142" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C142" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="D142" t="s">
         <v>230</v>
       </c>
       <c r="E142" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="F142" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="G142" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="H142" t="s">
         <v>925</v>
@@ -12648,28 +12650,28 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B143" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C143" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="D143" t="s">
         <v>12</v>
       </c>
       <c r="E143" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="F143" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="G143" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="H143" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="I143" t="s">
         <v>313</v>
@@ -12680,10 +12682,10 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B144" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C144" t="s">
         <v>213</v>
@@ -12692,13 +12694,13 @@
         <v>424</v>
       </c>
       <c r="E144" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="F144" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="G144" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="H144" t="s">
         <v>869</v>
@@ -12712,25 +12714,25 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B145" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C145" t="s">
         <v>244</v>
       </c>
       <c r="D145" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="E145" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="F145" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="G145" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="H145" t="s">
         <v>671</v>
@@ -12744,28 +12746,28 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B146" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C146" t="s">
         <v>556</v>
       </c>
       <c r="D146" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="E146" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="F146" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="G146" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="H146" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="I146" t="s">
         <v>551</v>
@@ -12776,25 +12778,25 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B147" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C147" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D147" t="s">
         <v>106</v>
       </c>
       <c r="E147" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="F147" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="G147" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="H147" t="s">
         <v>278</v>
@@ -12808,10 +12810,10 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B148" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C148" t="s">
         <v>11</v>
@@ -12820,16 +12822,16 @@
         <v>21</v>
       </c>
       <c r="E148" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="F148" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="G148" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="H148" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="I148" t="s">
         <v>187</v>
@@ -12840,10 +12842,10 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B149" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C149" t="s">
         <v>178</v>
@@ -12852,19 +12854,19 @@
         <v>989</v>
       </c>
       <c r="E149" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="F149" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="G149" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="H149" t="s">
         <v>85</v>
       </c>
       <c r="I149" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="J149">
         <v>15000</v>
@@ -12872,10 +12874,10 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B150" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C150" t="s">
         <v>966</v>
@@ -12884,16 +12886,16 @@
         <v>455</v>
       </c>
       <c r="E150" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="F150" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="G150" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="H150" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="I150" t="s">
         <v>249</v>
@@ -12904,25 +12906,25 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B151" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C151" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="D151" t="s">
         <v>21</v>
       </c>
       <c r="E151" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="F151" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="G151" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="H151" t="s">
         <v>298</v>
@@ -12936,10 +12938,10 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B152" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C152" t="s">
         <v>37</v>
@@ -12948,13 +12950,13 @@
         <v>21</v>
       </c>
       <c r="E152" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F152" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="G152" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="H152" t="s">
         <v>1061</v>
@@ -12968,28 +12970,28 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B153" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C153" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D153" t="s">
         <v>873</v>
       </c>
       <c r="E153" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="F153" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G153" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="H153" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="I153" t="s">
         <v>451</v>
@@ -13000,31 +13002,31 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B154" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C154" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="D154" t="s">
         <v>65</v>
       </c>
       <c r="E154" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="F154" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="G154" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="H154" t="s">
         <v>93</v>
       </c>
       <c r="I154" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="J154">
         <v>12000</v>
@@ -13032,25 +13034,25 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B155" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C155" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D155" t="s">
         <v>106</v>
       </c>
       <c r="E155" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="F155" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="G155" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="H155" t="s">
         <v>373</v>
@@ -13064,10 +13066,10 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B156" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C156" t="s">
         <v>105</v>
@@ -13076,19 +13078,19 @@
         <v>65</v>
       </c>
       <c r="E156" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="F156" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="G156" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="H156" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="I156" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="J156">
         <v>11000</v>
@@ -13096,25 +13098,25 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B157" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C157" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="D157" t="s">
         <v>65</v>
       </c>
       <c r="E157" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="F157" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="G157" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="H157" t="s">
         <v>515</v>
@@ -13128,25 +13130,25 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B158" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="C158" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="D158" t="s">
         <v>65</v>
       </c>
       <c r="E158" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="F158" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="G158" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="H158" t="s">
         <v>386</v>
@@ -13160,28 +13162,28 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B159" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C159" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="D159" t="s">
         <v>230</v>
       </c>
       <c r="E159" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F159" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="G159" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="H159" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="I159" t="s">
         <v>136</v>
@@ -13192,28 +13194,28 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B160" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C160" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="D160" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="E160" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="F160" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="G160" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="H160" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="I160" t="s">
         <v>912</v>
@@ -13224,10 +13226,10 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B161" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C161" t="s">
         <v>835</v>
@@ -13236,19 +13238,19 @@
         <v>21</v>
       </c>
       <c r="E161" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F161" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="G161" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="H161" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="I161" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="J161">
         <v>12000</v>
@@ -13256,28 +13258,28 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B162" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C162" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="D162" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="E162" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="F162" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="G162" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="H162" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="I162" t="s">
         <v>919</v>
@@ -13288,28 +13290,28 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B163" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C163" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="D163" t="s">
         <v>65</v>
       </c>
       <c r="E163" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="F163" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="G163" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="H163" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="I163" t="s">
         <v>572</v>
@@ -13320,28 +13322,28 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B164" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C164" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="D164" t="s">
         <v>989</v>
       </c>
       <c r="E164" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="F164" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="G164" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="H164" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="I164" t="s">
         <v>715</v>
@@ -13352,28 +13354,28 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B165" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C165" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="D165" t="s">
         <v>65</v>
       </c>
       <c r="E165" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="F165" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="G165" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="H165" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="I165" t="s">
         <v>258</v>
@@ -13384,10 +13386,10 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B166" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C166" t="s">
         <v>29</v>
@@ -13396,13 +13398,13 @@
         <v>65</v>
       </c>
       <c r="E166" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="F166" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G166" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="H166" t="s">
         <v>837</v>
@@ -13416,10 +13418,10 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B167" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C167" t="s">
         <v>190</v>
@@ -13428,13 +13430,13 @@
         <v>603</v>
       </c>
       <c r="E167" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="F167" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="G167" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="H167" t="s">
         <v>999</v>
@@ -13448,10 +13450,10 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B168" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C168" t="s">
         <v>190</v>
@@ -13460,13 +13462,13 @@
         <v>65</v>
       </c>
       <c r="E168" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="F168" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="G168" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="H168" t="s">
         <v>195</v>
@@ -13480,25 +13482,25 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B169" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C169" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="D169" t="s">
         <v>65</v>
       </c>
       <c r="E169" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="F169" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="G169" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="H169" t="s">
         <v>618</v>
@@ -13512,10 +13514,10 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B170" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C170" t="s">
         <v>790</v>
@@ -13524,13 +13526,13 @@
         <v>65</v>
       </c>
       <c r="E170" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="F170" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="G170" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H170" t="s">
         <v>664</v>
@@ -13544,10 +13546,10 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B171" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C171" t="s">
         <v>29</v>
@@ -13556,16 +13558,16 @@
         <v>65</v>
       </c>
       <c r="E171" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="F171" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G171" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H171" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="I171" t="s">
         <v>313</v>
@@ -13576,25 +13578,25 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="B172" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C172" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="D172" t="s">
         <v>230</v>
       </c>
       <c r="E172" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="F172" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="G172" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="H172" t="s">
         <v>587</v>
@@ -13608,25 +13610,25 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B173" t="s">
-        <v>1151</v>
+        <v>2571</v>
       </c>
       <c r="C173" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D173" t="s">
         <v>989</v>
       </c>
       <c r="E173" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F173" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G173" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H173" t="s">
         <v>925</v>
@@ -13640,28 +13642,28 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B174" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C174" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D174" t="s">
         <v>21</v>
       </c>
       <c r="E174" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F174" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G174" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H174" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I174" t="s">
         <v>94</v>
@@ -13672,10 +13674,10 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B175" t="s">
-        <v>1138</v>
+        <v>2572</v>
       </c>
       <c r="C175" t="s">
         <v>1137</v>
@@ -17224,10 +17226,10 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="B286" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="C286" t="s">
         <v>556</v>
@@ -17236,19 +17238,19 @@
         <v>568</v>
       </c>
       <c r="E286" t="s">
+        <v>1888</v>
+      </c>
+      <c r="F286" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G286" t="s">
         <v>1890</v>
-      </c>
-      <c r="F286" t="s">
-        <v>1891</v>
-      </c>
-      <c r="G286" t="s">
-        <v>1892</v>
       </c>
       <c r="H286" t="s">
         <v>217</v>
       </c>
       <c r="I286" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="J286">
         <v>16000</v>
@@ -17256,28 +17258,28 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="B287" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="C287" t="s">
         <v>809</v>
       </c>
       <c r="D287" t="s">
+        <v>1893</v>
+      </c>
+      <c r="E287" t="s">
+        <v>1894</v>
+      </c>
+      <c r="F287" t="s">
         <v>1895</v>
       </c>
-      <c r="E287" t="s">
+      <c r="G287" t="s">
         <v>1896</v>
       </c>
-      <c r="F287" t="s">
-        <v>1897</v>
-      </c>
-      <c r="G287" t="s">
-        <v>1898</v>
-      </c>
       <c r="H287" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="I287" t="s">
         <v>715</v>
@@ -17288,10 +17290,10 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="B288" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="C288" t="s">
         <v>720</v>
@@ -17300,16 +17302,16 @@
         <v>65</v>
       </c>
       <c r="E288" t="s">
+        <v>1899</v>
+      </c>
+      <c r="F288" t="s">
+        <v>1900</v>
+      </c>
+      <c r="G288" t="s">
         <v>1901</v>
       </c>
-      <c r="F288" t="s">
+      <c r="H288" t="s">
         <v>1902</v>
-      </c>
-      <c r="G288" t="s">
-        <v>1903</v>
-      </c>
-      <c r="H288" t="s">
-        <v>1904</v>
       </c>
       <c r="I288" t="s">
         <v>187</v>
@@ -17320,10 +17322,10 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="B289" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="C289" t="s">
         <v>29</v>
@@ -17332,13 +17334,13 @@
         <v>455</v>
       </c>
       <c r="E289" t="s">
+        <v>1905</v>
+      </c>
+      <c r="F289" t="s">
+        <v>1906</v>
+      </c>
+      <c r="G289" t="s">
         <v>1907</v>
-      </c>
-      <c r="F289" t="s">
-        <v>1908</v>
-      </c>
-      <c r="G289" t="s">
-        <v>1909</v>
       </c>
       <c r="H289" t="s">
         <v>786</v>
@@ -17352,25 +17354,25 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="B290" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="C290" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="D290" t="s">
         <v>65</v>
       </c>
       <c r="E290" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F290" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G290" t="s">
         <v>1912</v>
-      </c>
-      <c r="F290" t="s">
-        <v>1913</v>
-      </c>
-      <c r="G290" t="s">
-        <v>1914</v>
       </c>
       <c r="H290" t="s">
         <v>805</v>
@@ -17384,28 +17386,28 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="B291" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="C291" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="D291" t="s">
         <v>65</v>
       </c>
       <c r="E291" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F291" t="s">
+        <v>1916</v>
+      </c>
+      <c r="G291" t="s">
         <v>1917</v>
       </c>
-      <c r="F291" t="s">
-        <v>1918</v>
-      </c>
-      <c r="G291" t="s">
-        <v>1919</v>
-      </c>
       <c r="H291" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="I291" t="s">
         <v>111</v>
@@ -17416,10 +17418,10 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="B292" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="C292" t="s">
         <v>832</v>
@@ -17428,13 +17430,13 @@
         <v>65</v>
       </c>
       <c r="E292" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F292" t="s">
+        <v>1921</v>
+      </c>
+      <c r="G292" t="s">
         <v>1922</v>
-      </c>
-      <c r="F292" t="s">
-        <v>1923</v>
-      </c>
-      <c r="G292" t="s">
-        <v>1924</v>
       </c>
       <c r="H292" t="s">
         <v>694</v>
@@ -17448,25 +17450,25 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B293" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C293" t="s">
         <v>1925</v>
       </c>
-      <c r="B293" t="s">
+      <c r="D293" t="s">
         <v>1926</v>
       </c>
-      <c r="C293" t="s">
+      <c r="E293" t="s">
         <v>1927</v>
       </c>
-      <c r="D293" t="s">
+      <c r="F293" t="s">
         <v>1928</v>
       </c>
-      <c r="E293" t="s">
+      <c r="G293" t="s">
         <v>1929</v>
-      </c>
-      <c r="F293" t="s">
-        <v>1930</v>
-      </c>
-      <c r="G293" t="s">
-        <v>1931</v>
       </c>
       <c r="H293" t="s">
         <v>701</v>
@@ -17480,28 +17482,28 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="B294" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="C294" t="s">
         <v>131</v>
       </c>
       <c r="D294" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E294" t="s">
+        <v>1933</v>
+      </c>
+      <c r="F294" t="s">
         <v>1934</v>
       </c>
-      <c r="E294" t="s">
+      <c r="G294" t="s">
         <v>1935</v>
       </c>
-      <c r="F294" t="s">
+      <c r="H294" t="s">
         <v>1936</v>
-      </c>
-      <c r="G294" t="s">
-        <v>1937</v>
-      </c>
-      <c r="H294" t="s">
-        <v>1938</v>
       </c>
       <c r="I294" t="s">
         <v>17</v>
@@ -17512,10 +17514,10 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="B295" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="C295" t="s">
         <v>790</v>
@@ -17524,13 +17526,13 @@
         <v>21</v>
       </c>
       <c r="E295" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F295" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G295" t="s">
         <v>1941</v>
-      </c>
-      <c r="F295" t="s">
-        <v>1942</v>
-      </c>
-      <c r="G295" t="s">
-        <v>1943</v>
       </c>
       <c r="H295" t="s">
         <v>142</v>
@@ -17544,10 +17546,10 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="B296" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="C296" t="s">
         <v>29</v>
@@ -17556,16 +17558,16 @@
         <v>65</v>
       </c>
       <c r="E296" t="s">
+        <v>1944</v>
+      </c>
+      <c r="F296" t="s">
+        <v>1945</v>
+      </c>
+      <c r="G296" t="s">
         <v>1946</v>
       </c>
-      <c r="F296" t="s">
+      <c r="H296" t="s">
         <v>1947</v>
-      </c>
-      <c r="G296" t="s">
-        <v>1948</v>
-      </c>
-      <c r="H296" t="s">
-        <v>1949</v>
       </c>
       <c r="I296" t="s">
         <v>700</v>
@@ -17576,10 +17578,10 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="B297" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C297" t="s">
         <v>676</v>
@@ -17588,16 +17590,16 @@
         <v>568</v>
       </c>
       <c r="E297" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F297" t="s">
+        <v>1951</v>
+      </c>
+      <c r="G297" t="s">
         <v>1952</v>
       </c>
-      <c r="F297" t="s">
-        <v>1953</v>
-      </c>
-      <c r="G297" t="s">
-        <v>1954</v>
-      </c>
       <c r="H297" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="I297" t="s">
         <v>187</v>
@@ -17608,25 +17610,25 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B298" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="C298" t="s">
         <v>173</v>
       </c>
       <c r="D298" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E298" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F298" t="s">
         <v>1957</v>
       </c>
-      <c r="E298" t="s">
+      <c r="G298" t="s">
         <v>1958</v>
-      </c>
-      <c r="F298" t="s">
-        <v>1959</v>
-      </c>
-      <c r="G298" t="s">
-        <v>1960</v>
       </c>
       <c r="H298" t="s">
         <v>393</v>
@@ -17640,10 +17642,10 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B299" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="C299" t="s">
         <v>178</v>
@@ -17652,16 +17654,16 @@
         <v>748</v>
       </c>
       <c r="E299" t="s">
+        <v>1961</v>
+      </c>
+      <c r="F299" t="s">
+        <v>1962</v>
+      </c>
+      <c r="G299" t="s">
         <v>1963</v>
       </c>
-      <c r="F299" t="s">
-        <v>1964</v>
-      </c>
-      <c r="G299" t="s">
-        <v>1965</v>
-      </c>
       <c r="H299" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="I299" t="s">
         <v>715</v>
@@ -17672,10 +17674,10 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B300" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="C300" t="s">
         <v>178</v>
@@ -17684,13 +17686,13 @@
         <v>711</v>
       </c>
       <c r="E300" t="s">
+        <v>1966</v>
+      </c>
+      <c r="F300" t="s">
+        <v>1967</v>
+      </c>
+      <c r="G300" t="s">
         <v>1968</v>
-      </c>
-      <c r="F300" t="s">
-        <v>1969</v>
-      </c>
-      <c r="G300" t="s">
-        <v>1970</v>
       </c>
       <c r="H300" t="s">
         <v>349</v>
@@ -17704,28 +17706,28 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B301" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C301" t="s">
         <v>1971</v>
-      </c>
-      <c r="B301" t="s">
-        <v>1972</v>
-      </c>
-      <c r="C301" t="s">
-        <v>1973</v>
       </c>
       <c r="D301" t="s">
         <v>21</v>
       </c>
       <c r="E301" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F301" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G301" t="s">
         <v>1974</v>
       </c>
-      <c r="F301" t="s">
+      <c r="H301" t="s">
         <v>1975</v>
-      </c>
-      <c r="G301" t="s">
-        <v>1976</v>
-      </c>
-      <c r="H301" t="s">
-        <v>1977</v>
       </c>
       <c r="I301" t="s">
         <v>218</v>
@@ -17736,10 +17738,10 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B302" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="C302" t="s">
         <v>29</v>
@@ -17748,16 +17750,16 @@
         <v>21</v>
       </c>
       <c r="E302" t="s">
+        <v>1978</v>
+      </c>
+      <c r="F302" t="s">
+        <v>1979</v>
+      </c>
+      <c r="G302" t="s">
         <v>1980</v>
       </c>
-      <c r="F302" t="s">
+      <c r="H302" t="s">
         <v>1981</v>
-      </c>
-      <c r="G302" t="s">
-        <v>1982</v>
-      </c>
-      <c r="H302" t="s">
-        <v>1983</v>
       </c>
       <c r="I302" t="s">
         <v>218</v>
@@ -17768,25 +17770,25 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C303" t="s">
         <v>1984</v>
-      </c>
-      <c r="B303" t="s">
-        <v>1985</v>
-      </c>
-      <c r="C303" t="s">
-        <v>1986</v>
       </c>
       <c r="D303" t="s">
         <v>65</v>
       </c>
       <c r="E303" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F303" t="s">
+        <v>1986</v>
+      </c>
+      <c r="G303" t="s">
         <v>1987</v>
-      </c>
-      <c r="F303" t="s">
-        <v>1988</v>
-      </c>
-      <c r="G303" t="s">
-        <v>1989</v>
       </c>
       <c r="H303" t="s">
         <v>843</v>
@@ -17800,28 +17802,28 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B304" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C304" t="s">
         <v>1990</v>
-      </c>
-      <c r="B304" t="s">
-        <v>1991</v>
-      </c>
-      <c r="C304" t="s">
-        <v>1992</v>
       </c>
       <c r="D304" t="s">
         <v>21</v>
       </c>
       <c r="E304" t="s">
+        <v>1991</v>
+      </c>
+      <c r="F304" t="s">
+        <v>1992</v>
+      </c>
+      <c r="G304" t="s">
         <v>1993</v>
       </c>
-      <c r="F304" t="s">
+      <c r="H304" t="s">
         <v>1994</v>
-      </c>
-      <c r="G304" t="s">
-        <v>1995</v>
-      </c>
-      <c r="H304" t="s">
-        <v>1996</v>
       </c>
       <c r="I304" t="s">
         <v>572</v>
@@ -17832,10 +17834,10 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B305" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="C305" t="s">
         <v>178</v>
@@ -17844,13 +17846,13 @@
         <v>106</v>
       </c>
       <c r="E305" t="s">
+        <v>1997</v>
+      </c>
+      <c r="F305" t="s">
+        <v>1998</v>
+      </c>
+      <c r="G305" t="s">
         <v>1999</v>
-      </c>
-      <c r="F305" t="s">
-        <v>2000</v>
-      </c>
-      <c r="G305" t="s">
-        <v>2001</v>
       </c>
       <c r="H305" t="s">
         <v>265</v>
@@ -17864,10 +17866,10 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B306" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C306" t="s">
         <v>11</v>
@@ -17876,13 +17878,13 @@
         <v>989</v>
       </c>
       <c r="E306" t="s">
+        <v>2002</v>
+      </c>
+      <c r="F306" t="s">
+        <v>2003</v>
+      </c>
+      <c r="G306" t="s">
         <v>2004</v>
-      </c>
-      <c r="F306" t="s">
-        <v>2005</v>
-      </c>
-      <c r="G306" t="s">
-        <v>2006</v>
       </c>
       <c r="H306" t="s">
         <v>1074</v>
@@ -17899,28 +17901,28 @@
         <v>194405</v>
       </c>
       <c r="B307" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="C307" t="s">
         <v>178</v>
       </c>
       <c r="D307" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E307" t="s">
+        <v>2007</v>
+      </c>
+      <c r="F307" t="s">
         <v>2008</v>
       </c>
-      <c r="E307" t="s">
+      <c r="G307" t="s">
         <v>2009</v>
       </c>
-      <c r="F307" t="s">
-        <v>2010</v>
-      </c>
-      <c r="G307" t="s">
-        <v>2011</v>
-      </c>
       <c r="H307" s="2" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="J307">
         <v>14000</v>
@@ -17928,28 +17930,28 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B308" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C308" t="s">
         <v>676</v>
       </c>
       <c r="D308" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E308" t="s">
+        <v>2013</v>
+      </c>
+      <c r="F308" t="s">
         <v>2014</v>
       </c>
-      <c r="E308" t="s">
+      <c r="G308" t="s">
         <v>2015</v>
       </c>
-      <c r="F308" t="s">
-        <v>2016</v>
-      </c>
-      <c r="G308" t="s">
-        <v>2017</v>
-      </c>
       <c r="H308" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="I308" t="s">
         <v>1123</v>
@@ -17960,25 +17962,25 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B309" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C309" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="D309" t="s">
         <v>65</v>
       </c>
       <c r="E309" t="s">
+        <v>2018</v>
+      </c>
+      <c r="F309" t="s">
+        <v>2019</v>
+      </c>
+      <c r="G309" t="s">
         <v>2020</v>
-      </c>
-      <c r="F309" t="s">
-        <v>2021</v>
-      </c>
-      <c r="G309" t="s">
-        <v>2022</v>
       </c>
       <c r="H309" t="s">
         <v>587</v>
@@ -17992,25 +17994,25 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B310" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C310" t="s">
         <v>29</v>
       </c>
       <c r="D310" t="s">
+        <v>2023</v>
+      </c>
+      <c r="E310" t="s">
+        <v>2024</v>
+      </c>
+      <c r="F310" t="s">
         <v>2025</v>
       </c>
-      <c r="E310" t="s">
+      <c r="G310" t="s">
         <v>2026</v>
-      </c>
-      <c r="F310" t="s">
-        <v>2027</v>
-      </c>
-      <c r="G310" t="s">
-        <v>2028</v>
       </c>
       <c r="H310" t="s">
         <v>195</v>
@@ -18024,25 +18026,25 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B311" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C311" t="s">
         <v>2029</v>
-      </c>
-      <c r="B311" t="s">
-        <v>2030</v>
-      </c>
-      <c r="C311" t="s">
-        <v>2031</v>
       </c>
       <c r="D311" t="s">
         <v>768</v>
       </c>
       <c r="E311" t="s">
+        <v>2030</v>
+      </c>
+      <c r="F311" t="s">
+        <v>2031</v>
+      </c>
+      <c r="G311" t="s">
         <v>2032</v>
-      </c>
-      <c r="F311" t="s">
-        <v>2033</v>
-      </c>
-      <c r="G311" t="s">
-        <v>2034</v>
       </c>
       <c r="H311" t="s">
         <v>156</v>
@@ -18056,31 +18058,31 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="B312" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="C312" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="D312" t="s">
         <v>424</v>
       </c>
       <c r="E312" t="s">
+        <v>2035</v>
+      </c>
+      <c r="F312" t="s">
+        <v>2036</v>
+      </c>
+      <c r="G312" t="s">
         <v>2037</v>
       </c>
-      <c r="F312" t="s">
+      <c r="H312" t="s">
         <v>2038</v>
       </c>
-      <c r="G312" t="s">
-        <v>2039</v>
-      </c>
-      <c r="H312" t="s">
-        <v>2040</v>
-      </c>
       <c r="I312" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="J312">
         <v>9000</v>
@@ -18088,10 +18090,10 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="B313" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="C313" t="s">
         <v>29</v>
@@ -18100,13 +18102,13 @@
         <v>21</v>
       </c>
       <c r="E313" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F313" t="s">
+        <v>2042</v>
+      </c>
+      <c r="G313" t="s">
         <v>2043</v>
-      </c>
-      <c r="F313" t="s">
-        <v>2044</v>
-      </c>
-      <c r="G313" t="s">
-        <v>2045</v>
       </c>
       <c r="H313" t="s">
         <v>119</v>
@@ -18120,10 +18122,10 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="B314" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="C314" t="s">
         <v>37</v>
@@ -18132,19 +18134,19 @@
         <v>65</v>
       </c>
       <c r="E314" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F314" t="s">
+        <v>2047</v>
+      </c>
+      <c r="G314" t="s">
         <v>2048</v>
       </c>
-      <c r="F314" t="s">
-        <v>2049</v>
-      </c>
-      <c r="G314" t="s">
-        <v>2050</v>
-      </c>
       <c r="H314" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="I314" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="J314">
         <v>9000</v>
@@ -18152,10 +18154,10 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="B315" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="C315" t="s">
         <v>11</v>
@@ -18164,16 +18166,16 @@
         <v>21</v>
       </c>
       <c r="E315" t="s">
+        <v>2051</v>
+      </c>
+      <c r="F315" t="s">
+        <v>2052</v>
+      </c>
+      <c r="G315" t="s">
         <v>2053</v>
       </c>
-      <c r="F315" t="s">
-        <v>2054</v>
-      </c>
-      <c r="G315" t="s">
-        <v>2055</v>
-      </c>
       <c r="H315" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="I315" t="s">
         <v>919</v>
@@ -18184,10 +18186,10 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="B316" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="C316" t="s">
         <v>361</v>
@@ -18196,19 +18198,19 @@
         <v>106</v>
       </c>
       <c r="E316" t="s">
+        <v>2056</v>
+      </c>
+      <c r="F316" t="s">
+        <v>2057</v>
+      </c>
+      <c r="G316" t="s">
         <v>2058</v>
       </c>
-      <c r="F316" t="s">
-        <v>2059</v>
-      </c>
-      <c r="G316" t="s">
-        <v>2060</v>
-      </c>
       <c r="H316" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="I316" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="J316">
         <v>18000</v>
@@ -18216,10 +18218,10 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="B317" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="C317" t="s">
         <v>782</v>
@@ -18228,16 +18230,16 @@
         <v>568</v>
       </c>
       <c r="E317" t="s">
+        <v>2061</v>
+      </c>
+      <c r="F317" t="s">
+        <v>2062</v>
+      </c>
+      <c r="G317" t="s">
         <v>2063</v>
       </c>
-      <c r="F317" t="s">
-        <v>2064</v>
-      </c>
-      <c r="G317" t="s">
-        <v>2065</v>
-      </c>
       <c r="H317" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I317" t="s">
         <v>26</v>
@@ -18248,10 +18250,10 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="B318" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="C318" t="s">
         <v>29</v>
@@ -18260,13 +18262,13 @@
         <v>302</v>
       </c>
       <c r="E318" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F318" t="s">
+        <v>2067</v>
+      </c>
+      <c r="G318" t="s">
         <v>2068</v>
-      </c>
-      <c r="F318" t="s">
-        <v>2069</v>
-      </c>
-      <c r="G318" t="s">
-        <v>2070</v>
       </c>
       <c r="H318" t="s">
         <v>393</v>
@@ -18280,25 +18282,25 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B319" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C319" t="s">
         <v>2071</v>
-      </c>
-      <c r="B319" t="s">
-        <v>2072</v>
-      </c>
-      <c r="C319" t="s">
-        <v>2073</v>
       </c>
       <c r="D319" t="s">
         <v>526</v>
       </c>
       <c r="E319" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F319" t="s">
+        <v>2073</v>
+      </c>
+      <c r="G319" t="s">
         <v>2074</v>
-      </c>
-      <c r="F319" t="s">
-        <v>2075</v>
-      </c>
-      <c r="G319" t="s">
-        <v>2076</v>
       </c>
       <c r="H319" t="s">
         <v>393</v>
@@ -18312,31 +18314,31 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="B320" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="C320" t="s">
         <v>11</v>
       </c>
       <c r="D320" t="s">
+        <v>2077</v>
+      </c>
+      <c r="E320" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F320" t="s">
         <v>2079</v>
       </c>
-      <c r="E320" t="s">
+      <c r="G320" t="s">
         <v>2080</v>
       </c>
-      <c r="F320" t="s">
-        <v>2081</v>
-      </c>
-      <c r="G320" t="s">
-        <v>2082</v>
-      </c>
       <c r="H320" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="I320" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="J320">
         <v>12000</v>
@@ -18344,28 +18346,28 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="B321" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="C321" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="D321" t="s">
         <v>106</v>
       </c>
       <c r="E321" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F321" t="s">
+        <v>2084</v>
+      </c>
+      <c r="G321" t="s">
         <v>2085</v>
       </c>
-      <c r="F321" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G321" t="s">
-        <v>2087</v>
-      </c>
       <c r="H321" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="I321" t="s">
         <v>739</v>
@@ -18376,10 +18378,10 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="B322" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="C322" t="s">
         <v>676</v>
@@ -18388,13 +18390,13 @@
         <v>65</v>
       </c>
       <c r="E322" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F322" t="s">
+        <v>2089</v>
+      </c>
+      <c r="G322" t="s">
         <v>2090</v>
-      </c>
-      <c r="F322" t="s">
-        <v>2091</v>
-      </c>
-      <c r="G322" t="s">
-        <v>2092</v>
       </c>
       <c r="H322" t="s">
         <v>217</v>
@@ -18408,25 +18410,25 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="B323" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="C323" t="s">
         <v>790</v>
       </c>
       <c r="D323" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E323" t="s">
+        <v>2094</v>
+      </c>
+      <c r="F323" t="s">
         <v>2095</v>
       </c>
-      <c r="E323" t="s">
+      <c r="G323" t="s">
         <v>2096</v>
-      </c>
-      <c r="F323" t="s">
-        <v>2097</v>
-      </c>
-      <c r="G323" t="s">
-        <v>2098</v>
       </c>
       <c r="H323" t="s">
         <v>501</v>
@@ -18440,25 +18442,25 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B324" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C324" t="s">
         <v>2099</v>
-      </c>
-      <c r="B324" t="s">
-        <v>2100</v>
-      </c>
-      <c r="C324" t="s">
-        <v>2101</v>
       </c>
       <c r="D324" t="s">
         <v>230</v>
       </c>
       <c r="E324" t="s">
+        <v>2100</v>
+      </c>
+      <c r="F324" t="s">
+        <v>2101</v>
+      </c>
+      <c r="G324" t="s">
         <v>2102</v>
-      </c>
-      <c r="F324" t="s">
-        <v>2103</v>
-      </c>
-      <c r="G324" t="s">
-        <v>2104</v>
       </c>
       <c r="H324" t="s">
         <v>679</v>
@@ -18472,10 +18474,10 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="B325" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="C325" t="s">
         <v>853</v>
@@ -18484,13 +18486,13 @@
         <v>230</v>
       </c>
       <c r="E325" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F325" t="s">
+        <v>2106</v>
+      </c>
+      <c r="G325" t="s">
         <v>2107</v>
-      </c>
-      <c r="F325" t="s">
-        <v>2108</v>
-      </c>
-      <c r="G325" t="s">
-        <v>2109</v>
       </c>
       <c r="H325" t="s">
         <v>716</v>
@@ -18504,28 +18506,28 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="B326" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="C326" t="s">
         <v>464</v>
       </c>
       <c r="D326" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E326" t="s">
+        <v>2111</v>
+      </c>
+      <c r="F326" t="s">
         <v>2112</v>
       </c>
-      <c r="E326" t="s">
+      <c r="G326" t="s">
         <v>2113</v>
       </c>
-      <c r="F326" t="s">
+      <c r="H326" t="s">
         <v>2114</v>
-      </c>
-      <c r="G326" t="s">
-        <v>2115</v>
-      </c>
-      <c r="H326" t="s">
-        <v>2116</v>
       </c>
       <c r="I326" t="s">
         <v>52</v>
@@ -18536,25 +18538,25 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="B327" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="C327" t="s">
         <v>676</v>
       </c>
       <c r="D327" t="s">
+        <v>2117</v>
+      </c>
+      <c r="E327" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F327" t="s">
         <v>2119</v>
       </c>
-      <c r="E327" t="s">
+      <c r="G327" t="s">
         <v>2120</v>
-      </c>
-      <c r="F327" t="s">
-        <v>2121</v>
-      </c>
-      <c r="G327" t="s">
-        <v>2122</v>
       </c>
       <c r="H327" t="s">
         <v>843</v>
@@ -18568,25 +18570,25 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="B328" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="C328" t="s">
         <v>630</v>
       </c>
       <c r="D328" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E328" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F328" t="s">
         <v>2125</v>
       </c>
-      <c r="E328" t="s">
+      <c r="G328" t="s">
         <v>2126</v>
-      </c>
-      <c r="F328" t="s">
-        <v>2127</v>
-      </c>
-      <c r="G328" t="s">
-        <v>2128</v>
       </c>
       <c r="H328" t="s">
         <v>744</v>
@@ -18600,25 +18602,25 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="B329" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="C329" t="s">
         <v>37</v>
       </c>
       <c r="D329" t="s">
+        <v>2129</v>
+      </c>
+      <c r="E329" t="s">
+        <v>2130</v>
+      </c>
+      <c r="F329" t="s">
         <v>2131</v>
       </c>
-      <c r="E329" t="s">
+      <c r="G329" t="s">
         <v>2132</v>
-      </c>
-      <c r="F329" t="s">
-        <v>2133</v>
-      </c>
-      <c r="G329" t="s">
-        <v>2134</v>
       </c>
       <c r="H329" t="s">
         <v>399</v>
@@ -18632,10 +18634,10 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="B330" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="C330" t="s">
         <v>190</v>
@@ -18644,16 +18646,16 @@
         <v>362</v>
       </c>
       <c r="E330" t="s">
+        <v>2135</v>
+      </c>
+      <c r="F330" t="s">
+        <v>2136</v>
+      </c>
+      <c r="G330" t="s">
         <v>2137</v>
       </c>
-      <c r="F330" t="s">
+      <c r="H330" t="s">
         <v>2138</v>
-      </c>
-      <c r="G330" t="s">
-        <v>2139</v>
-      </c>
-      <c r="H330" t="s">
-        <v>2140</v>
       </c>
       <c r="I330" t="s">
         <v>451</v>
@@ -18664,31 +18666,31 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="B331" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="C331" t="s">
         <v>29</v>
       </c>
       <c r="D331" t="s">
+        <v>2141</v>
+      </c>
+      <c r="E331" t="s">
+        <v>2142</v>
+      </c>
+      <c r="F331" t="s">
         <v>2143</v>
       </c>
-      <c r="E331" t="s">
+      <c r="G331" t="s">
         <v>2144</v>
       </c>
-      <c r="F331" t="s">
-        <v>2145</v>
-      </c>
-      <c r="G331" t="s">
-        <v>2146</v>
-      </c>
       <c r="H331" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="I331" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="J331">
         <v>11000</v>
@@ -18696,10 +18698,10 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="B332" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="C332" t="s">
         <v>11</v>
@@ -18708,16 +18710,16 @@
         <v>65</v>
       </c>
       <c r="E332" t="s">
+        <v>2147</v>
+      </c>
+      <c r="F332" t="s">
+        <v>2148</v>
+      </c>
+      <c r="G332" t="s">
         <v>2149</v>
       </c>
-      <c r="F332" t="s">
+      <c r="H332" t="s">
         <v>2150</v>
-      </c>
-      <c r="G332" t="s">
-        <v>2151</v>
-      </c>
-      <c r="H332" t="s">
-        <v>2152</v>
       </c>
       <c r="I332" t="s">
         <v>61</v>
@@ -18728,10 +18730,10 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="B333" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="C333" t="s">
         <v>29</v>
@@ -18740,16 +18742,16 @@
         <v>661</v>
       </c>
       <c r="E333" t="s">
+        <v>2153</v>
+      </c>
+      <c r="F333" t="s">
+        <v>2154</v>
+      </c>
+      <c r="G333" t="s">
         <v>2155</v>
       </c>
-      <c r="F333" t="s">
+      <c r="H333" t="s">
         <v>2156</v>
-      </c>
-      <c r="G333" t="s">
-        <v>2157</v>
-      </c>
-      <c r="H333" t="s">
-        <v>2158</v>
       </c>
       <c r="I333" t="s">
         <v>128</v>
@@ -18760,28 +18762,28 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B334" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C334" t="s">
         <v>2159</v>
-      </c>
-      <c r="B334" t="s">
-        <v>2160</v>
-      </c>
-      <c r="C334" t="s">
-        <v>2161</v>
       </c>
       <c r="D334" t="s">
         <v>603</v>
       </c>
       <c r="E334" t="s">
+        <v>2160</v>
+      </c>
+      <c r="F334" t="s">
+        <v>2161</v>
+      </c>
+      <c r="G334" t="s">
         <v>2162</v>
       </c>
-      <c r="F334" t="s">
+      <c r="H334" t="s">
         <v>2163</v>
-      </c>
-      <c r="G334" t="s">
-        <v>2164</v>
-      </c>
-      <c r="H334" t="s">
-        <v>2165</v>
       </c>
       <c r="I334" t="s">
         <v>820</v>
@@ -18792,28 +18794,28 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B335" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C335" t="s">
         <v>2166</v>
-      </c>
-      <c r="B335" t="s">
-        <v>2167</v>
-      </c>
-      <c r="C335" t="s">
-        <v>2168</v>
       </c>
       <c r="D335" t="s">
         <v>424</v>
       </c>
       <c r="E335" t="s">
+        <v>2167</v>
+      </c>
+      <c r="F335" t="s">
+        <v>2168</v>
+      </c>
+      <c r="G335" t="s">
         <v>2169</v>
       </c>
-      <c r="F335" t="s">
+      <c r="H335" t="s">
         <v>2170</v>
-      </c>
-      <c r="G335" t="s">
-        <v>2171</v>
-      </c>
-      <c r="H335" t="s">
-        <v>2172</v>
       </c>
       <c r="I335" t="s">
         <v>61</v>
@@ -18824,28 +18826,28 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B336" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C336" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D336" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E336" t="s">
         <v>2173</v>
       </c>
-      <c r="B336" t="s">
+      <c r="F336" t="s">
         <v>2174</v>
       </c>
-      <c r="C336" t="s">
-        <v>1818</v>
-      </c>
-      <c r="D336" t="s">
-        <v>2095</v>
-      </c>
-      <c r="E336" t="s">
+      <c r="G336" t="s">
         <v>2175</v>
       </c>
-      <c r="F336" t="s">
+      <c r="H336" t="s">
         <v>2176</v>
-      </c>
-      <c r="G336" t="s">
-        <v>2177</v>
-      </c>
-      <c r="H336" t="s">
-        <v>2178</v>
       </c>
       <c r="I336" t="s">
         <v>226</v>
@@ -18856,28 +18858,28 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="B337" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="C337" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="D337" t="s">
         <v>302</v>
       </c>
       <c r="E337" t="s">
+        <v>2179</v>
+      </c>
+      <c r="F337" t="s">
+        <v>2180</v>
+      </c>
+      <c r="G337" t="s">
         <v>2181</v>
       </c>
-      <c r="F337" t="s">
-        <v>2182</v>
-      </c>
-      <c r="G337" t="s">
-        <v>2183</v>
-      </c>
       <c r="H337" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="I337" t="s">
         <v>321</v>
@@ -18888,28 +18890,28 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B338" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C338" t="s">
         <v>2184</v>
-      </c>
-      <c r="B338" t="s">
-        <v>2185</v>
-      </c>
-      <c r="C338" t="s">
-        <v>2186</v>
       </c>
       <c r="D338" t="s">
         <v>526</v>
       </c>
       <c r="E338" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F338" t="s">
+        <v>2186</v>
+      </c>
+      <c r="G338" t="s">
         <v>2187</v>
       </c>
-      <c r="F338" t="s">
-        <v>2188</v>
-      </c>
-      <c r="G338" t="s">
-        <v>2189</v>
-      </c>
       <c r="H338" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="I338" t="s">
         <v>17</v>
@@ -18920,28 +18922,28 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B339" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C339" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D339" t="s">
         <v>2190</v>
       </c>
-      <c r="B339" t="s">
+      <c r="E339" t="s">
         <v>2191</v>
       </c>
-      <c r="C339" t="s">
-        <v>1586</v>
-      </c>
-      <c r="D339" t="s">
+      <c r="F339" t="s">
         <v>2192</v>
       </c>
-      <c r="E339" t="s">
+      <c r="G339" t="s">
         <v>2193</v>
       </c>
-      <c r="F339" t="s">
+      <c r="H339" t="s">
         <v>2194</v>
-      </c>
-      <c r="G339" t="s">
-        <v>2195</v>
-      </c>
-      <c r="H339" t="s">
-        <v>2196</v>
       </c>
       <c r="I339" t="s">
         <v>26</v>
@@ -18952,28 +18954,28 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B340" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C340" t="s">
         <v>2197</v>
       </c>
-      <c r="B340" t="s">
+      <c r="D340" t="s">
         <v>2198</v>
       </c>
-      <c r="C340" t="s">
+      <c r="E340" t="s">
         <v>2199</v>
       </c>
-      <c r="D340" t="s">
+      <c r="F340" t="s">
         <v>2200</v>
       </c>
-      <c r="E340" t="s">
+      <c r="G340" t="s">
         <v>2201</v>
       </c>
-      <c r="F340" t="s">
-        <v>2202</v>
-      </c>
-      <c r="G340" t="s">
-        <v>2203</v>
-      </c>
       <c r="H340" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="I340" t="s">
         <v>321</v>
@@ -18984,10 +18986,10 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="B341" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C341" t="s">
         <v>11</v>
@@ -18996,16 +18998,16 @@
         <v>526</v>
       </c>
       <c r="E341" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F341" t="s">
+        <v>2205</v>
+      </c>
+      <c r="G341" t="s">
         <v>2206</v>
       </c>
-      <c r="F341" t="s">
-        <v>2207</v>
-      </c>
-      <c r="G341" t="s">
-        <v>2208</v>
-      </c>
       <c r="H341" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="I341" t="s">
         <v>34</v>
@@ -19016,10 +19018,10 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="B342" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="C342" t="s">
         <v>261</v>
@@ -19028,16 +19030,16 @@
         <v>577</v>
       </c>
       <c r="E342" t="s">
+        <v>2209</v>
+      </c>
+      <c r="F342" t="s">
+        <v>2210</v>
+      </c>
+      <c r="G342" t="s">
         <v>2211</v>
       </c>
-      <c r="F342" t="s">
-        <v>2212</v>
-      </c>
-      <c r="G342" t="s">
-        <v>2213</v>
-      </c>
       <c r="H342" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="I342" t="s">
         <v>912</v>
@@ -19048,31 +19050,31 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B343" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C343" t="s">
         <v>2214</v>
       </c>
-      <c r="B343" t="s">
+      <c r="D343" t="s">
         <v>2215</v>
       </c>
-      <c r="C343" t="s">
+      <c r="E343" t="s">
         <v>2216</v>
       </c>
-      <c r="D343" t="s">
+      <c r="F343" t="s">
         <v>2217</v>
       </c>
-      <c r="E343" t="s">
+      <c r="G343" t="s">
         <v>2218</v>
       </c>
-      <c r="F343" t="s">
+      <c r="H343" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I343" t="s">
         <v>2219</v>
-      </c>
-      <c r="G343" t="s">
-        <v>2220</v>
-      </c>
-      <c r="H343" t="s">
-        <v>1159</v>
-      </c>
-      <c r="I343" t="s">
-        <v>2221</v>
       </c>
       <c r="J343">
         <v>17000</v>
@@ -19080,31 +19082,31 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B344" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C344" t="s">
         <v>2222</v>
       </c>
-      <c r="B344" t="s">
+      <c r="D344" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E344" t="s">
         <v>2223</v>
       </c>
-      <c r="C344" t="s">
+      <c r="F344" t="s">
         <v>2224</v>
       </c>
-      <c r="D344" t="s">
-        <v>1772</v>
-      </c>
-      <c r="E344" t="s">
+      <c r="G344" t="s">
         <v>2225</v>
-      </c>
-      <c r="F344" t="s">
-        <v>2226</v>
-      </c>
-      <c r="G344" t="s">
-        <v>2227</v>
       </c>
       <c r="H344" t="s">
         <v>1043</v>
       </c>
       <c r="I344" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="J344">
         <v>15000</v>
@@ -19112,10 +19114,10 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="B345" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="C345" t="s">
         <v>97</v>
@@ -19124,13 +19126,13 @@
         <v>72</v>
       </c>
       <c r="E345" t="s">
+        <v>2229</v>
+      </c>
+      <c r="F345" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G345" t="s">
         <v>2231</v>
-      </c>
-      <c r="F345" t="s">
-        <v>2232</v>
-      </c>
-      <c r="G345" t="s">
-        <v>2233</v>
       </c>
       <c r="H345" t="s">
         <v>399</v>
@@ -19144,10 +19146,10 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="B346" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="C346" t="s">
         <v>418</v>
@@ -19156,16 +19158,16 @@
         <v>65</v>
       </c>
       <c r="E346" t="s">
+        <v>2234</v>
+      </c>
+      <c r="F346" t="s">
+        <v>2235</v>
+      </c>
+      <c r="G346" t="s">
         <v>2236</v>
       </c>
-      <c r="F346" t="s">
+      <c r="H346" t="s">
         <v>2237</v>
-      </c>
-      <c r="G346" t="s">
-        <v>2238</v>
-      </c>
-      <c r="H346" t="s">
-        <v>2239</v>
       </c>
       <c r="I346" t="s">
         <v>1123</v>
@@ -19176,28 +19178,28 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="B347" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="C347" t="s">
         <v>178</v>
       </c>
       <c r="D347" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E347" t="s">
+        <v>2241</v>
+      </c>
+      <c r="F347" t="s">
         <v>2242</v>
       </c>
-      <c r="E347" t="s">
+      <c r="G347" t="s">
         <v>2243</v>
       </c>
-      <c r="F347" t="s">
-        <v>2244</v>
-      </c>
-      <c r="G347" t="s">
-        <v>2245</v>
-      </c>
       <c r="H347" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="I347" t="s">
         <v>94</v>
@@ -19208,10 +19210,10 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="B348" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="C348" t="s">
         <v>178</v>
@@ -19220,16 +19222,16 @@
         <v>230</v>
       </c>
       <c r="E348" t="s">
+        <v>2246</v>
+      </c>
+      <c r="F348" t="s">
+        <v>2247</v>
+      </c>
+      <c r="G348" t="s">
         <v>2248</v>
       </c>
-      <c r="F348" t="s">
-        <v>2249</v>
-      </c>
-      <c r="G348" t="s">
-        <v>2250</v>
-      </c>
       <c r="H348" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="I348" t="s">
         <v>358</v>
@@ -19240,10 +19242,10 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="B349" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="C349" t="s">
         <v>29</v>
@@ -19252,19 +19254,19 @@
         <v>65</v>
       </c>
       <c r="E349" t="s">
+        <v>2251</v>
+      </c>
+      <c r="F349" t="s">
+        <v>2252</v>
+      </c>
+      <c r="G349" t="s">
         <v>2253</v>
-      </c>
-      <c r="F349" t="s">
-        <v>2254</v>
-      </c>
-      <c r="G349" t="s">
-        <v>2255</v>
       </c>
       <c r="H349" t="s">
         <v>701</v>
       </c>
       <c r="I349" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="J349">
         <v>13000</v>
@@ -19272,10 +19274,10 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="B350" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="C350" t="s">
         <v>11</v>
@@ -19284,13 +19286,13 @@
         <v>526</v>
       </c>
       <c r="E350" t="s">
+        <v>2256</v>
+      </c>
+      <c r="F350" t="s">
+        <v>2257</v>
+      </c>
+      <c r="G350" t="s">
         <v>2258</v>
-      </c>
-      <c r="F350" t="s">
-        <v>2259</v>
-      </c>
-      <c r="G350" t="s">
-        <v>2260</v>
       </c>
       <c r="H350" t="s">
         <v>1074</v>
@@ -19304,31 +19306,31 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B351" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C351" t="s">
         <v>2261</v>
       </c>
-      <c r="B351" t="s">
+      <c r="D351" t="s">
         <v>2262</v>
       </c>
-      <c r="C351" t="s">
+      <c r="E351" t="s">
         <v>2263</v>
       </c>
-      <c r="D351" t="s">
+      <c r="F351" t="s">
         <v>2264</v>
       </c>
-      <c r="E351" t="s">
+      <c r="G351" t="s">
         <v>2265</v>
       </c>
-      <c r="F351" t="s">
+      <c r="H351" t="s">
         <v>2266</v>
       </c>
-      <c r="G351" t="s">
-        <v>2267</v>
-      </c>
-      <c r="H351" t="s">
-        <v>2268</v>
-      </c>
       <c r="I351" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="J351">
         <v>18000</v>
@@ -19336,10 +19338,10 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="B352" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="C352" t="s">
         <v>287</v>
@@ -19348,16 +19350,16 @@
         <v>65</v>
       </c>
       <c r="E352" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F352" t="s">
+        <v>2270</v>
+      </c>
+      <c r="G352" t="s">
         <v>2271</v>
       </c>
-      <c r="F352" t="s">
-        <v>2272</v>
-      </c>
-      <c r="G352" t="s">
-        <v>2273</v>
-      </c>
       <c r="H352" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="I352" t="s">
         <v>17</v>
@@ -19368,25 +19370,25 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B353" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C353" t="s">
         <v>2274</v>
-      </c>
-      <c r="B353" t="s">
-        <v>2275</v>
-      </c>
-      <c r="C353" t="s">
-        <v>2276</v>
       </c>
       <c r="D353" t="s">
         <v>65</v>
       </c>
       <c r="E353" t="s">
+        <v>2275</v>
+      </c>
+      <c r="F353" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G353" t="s">
         <v>2277</v>
-      </c>
-      <c r="F353" t="s">
-        <v>2278</v>
-      </c>
-      <c r="G353" t="s">
-        <v>2279</v>
       </c>
       <c r="H353" t="s">
         <v>284</v>
@@ -19400,10 +19402,10 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>2280</v>
+        <v>2278</v>
       </c>
       <c r="B354" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="C354" t="s">
         <v>472</v>
@@ -19412,13 +19414,13 @@
         <v>106</v>
       </c>
       <c r="E354" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F354" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G354" t="s">
         <v>2282</v>
-      </c>
-      <c r="F354" t="s">
-        <v>2283</v>
-      </c>
-      <c r="G354" t="s">
-        <v>2284</v>
       </c>
       <c r="H354" t="s">
         <v>651</v>
@@ -19432,10 +19434,10 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="B355" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="C355" t="s">
         <v>954</v>
@@ -19444,13 +19446,13 @@
         <v>642</v>
       </c>
       <c r="E355" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F355" t="s">
+        <v>2286</v>
+      </c>
+      <c r="G355" t="s">
         <v>2287</v>
-      </c>
-      <c r="F355" t="s">
-        <v>2288</v>
-      </c>
-      <c r="G355" t="s">
-        <v>2289</v>
       </c>
       <c r="H355" t="s">
         <v>93</v>
@@ -19464,28 +19466,28 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
       <c r="B356" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C356" t="s">
         <v>1108</v>
       </c>
       <c r="D356" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="E356" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F356" t="s">
+        <v>2291</v>
+      </c>
+      <c r="G356" t="s">
         <v>2292</v>
       </c>
-      <c r="F356" t="s">
+      <c r="H356" t="s">
         <v>2293</v>
-      </c>
-      <c r="G356" t="s">
-        <v>2294</v>
-      </c>
-      <c r="H356" t="s">
-        <v>2295</v>
       </c>
       <c r="I356" t="s">
         <v>350</v>
@@ -19496,31 +19498,31 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B357" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C357" t="s">
         <v>2296</v>
-      </c>
-      <c r="B357" t="s">
-        <v>2297</v>
-      </c>
-      <c r="C357" t="s">
-        <v>2298</v>
       </c>
       <c r="D357" t="s">
         <v>106</v>
       </c>
       <c r="E357" t="s">
+        <v>2297</v>
+      </c>
+      <c r="F357" t="s">
+        <v>2298</v>
+      </c>
+      <c r="G357" t="s">
         <v>2299</v>
-      </c>
-      <c r="F357" t="s">
-        <v>2300</v>
-      </c>
-      <c r="G357" t="s">
-        <v>2301</v>
       </c>
       <c r="H357" t="s">
         <v>508</v>
       </c>
       <c r="I357" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="J357">
         <v>16000</v>
@@ -19528,25 +19530,25 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="B358" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="C358" t="s">
         <v>390</v>
       </c>
       <c r="D358" t="s">
+        <v>2302</v>
+      </c>
+      <c r="E358" t="s">
+        <v>2303</v>
+      </c>
+      <c r="F358" t="s">
         <v>2304</v>
       </c>
-      <c r="E358" t="s">
+      <c r="G358" t="s">
         <v>2305</v>
-      </c>
-      <c r="F358" t="s">
-        <v>2306</v>
-      </c>
-      <c r="G358" t="s">
-        <v>2307</v>
       </c>
       <c r="H358" t="s">
         <v>744</v>
@@ -19560,10 +19562,10 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="B359" t="s">
-        <v>2309</v>
+        <v>2307</v>
       </c>
       <c r="C359" t="s">
         <v>173</v>
@@ -19572,19 +19574,19 @@
         <v>72</v>
       </c>
       <c r="E359" t="s">
+        <v>2308</v>
+      </c>
+      <c r="F359" t="s">
+        <v>2309</v>
+      </c>
+      <c r="G359" t="s">
         <v>2310</v>
-      </c>
-      <c r="F359" t="s">
-        <v>2311</v>
-      </c>
-      <c r="G359" t="s">
-        <v>2312</v>
       </c>
       <c r="H359" t="s">
         <v>716</v>
       </c>
       <c r="I359" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="J359">
         <v>8000</v>
@@ -19592,28 +19594,28 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="B360" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="C360" t="s">
         <v>237</v>
       </c>
       <c r="D360" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="E360" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F360" t="s">
+        <v>2314</v>
+      </c>
+      <c r="G360" t="s">
         <v>2315</v>
       </c>
-      <c r="F360" t="s">
-        <v>2316</v>
-      </c>
-      <c r="G360" t="s">
-        <v>2317</v>
-      </c>
       <c r="H360" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="I360" t="s">
         <v>1035</v>
@@ -19624,10 +19626,10 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="B361" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="C361" t="s">
         <v>615</v>
@@ -19636,13 +19638,13 @@
         <v>65</v>
       </c>
       <c r="E361" t="s">
+        <v>2318</v>
+      </c>
+      <c r="F361" t="s">
+        <v>2319</v>
+      </c>
+      <c r="G361" t="s">
         <v>2320</v>
-      </c>
-      <c r="F361" t="s">
-        <v>2321</v>
-      </c>
-      <c r="G361" t="s">
-        <v>2322</v>
       </c>
       <c r="H361" t="s">
         <v>284</v>
@@ -19656,28 +19658,28 @@
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B362" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C362" t="s">
         <v>2323</v>
-      </c>
-      <c r="B362" t="s">
-        <v>2324</v>
-      </c>
-      <c r="C362" t="s">
-        <v>2325</v>
       </c>
       <c r="D362" t="s">
         <v>65</v>
       </c>
       <c r="E362" t="s">
+        <v>2324</v>
+      </c>
+      <c r="F362" t="s">
+        <v>2325</v>
+      </c>
+      <c r="G362" t="s">
         <v>2326</v>
       </c>
-      <c r="F362" t="s">
-        <v>2327</v>
-      </c>
-      <c r="G362" t="s">
-        <v>2328</v>
-      </c>
       <c r="H362" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="I362" t="s">
         <v>111</v>
@@ -19688,10 +19690,10 @@
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="B363" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="C363" t="s">
         <v>728</v>
@@ -19700,13 +19702,13 @@
         <v>603</v>
       </c>
       <c r="E363" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="F363" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="G363" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="H363" t="s">
         <v>843</v>
@@ -19720,10 +19722,10 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="B364" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="C364" t="s">
         <v>309</v>
@@ -19732,19 +19734,19 @@
         <v>748</v>
       </c>
       <c r="E364" t="s">
+        <v>2333</v>
+      </c>
+      <c r="F364" t="s">
+        <v>2334</v>
+      </c>
+      <c r="G364" t="s">
         <v>2335</v>
       </c>
-      <c r="F364" t="s">
-        <v>2336</v>
-      </c>
-      <c r="G364" t="s">
-        <v>2337</v>
-      </c>
       <c r="H364" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I364" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="J364">
         <v>13000</v>
@@ -19752,31 +19754,31 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="B365" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="C365" t="s">
         <v>123</v>
       </c>
       <c r="D365" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="E365" t="s">
+        <v>2338</v>
+      </c>
+      <c r="F365" t="s">
+        <v>2339</v>
+      </c>
+      <c r="G365" t="s">
         <v>2340</v>
       </c>
-      <c r="F365" t="s">
-        <v>2341</v>
-      </c>
-      <c r="G365" t="s">
-        <v>2342</v>
-      </c>
       <c r="H365" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="I365" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="J365">
         <v>18000</v>
@@ -19784,10 +19786,10 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="B366" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="C366" t="s">
         <v>622</v>
@@ -19796,16 +19798,16 @@
         <v>505</v>
       </c>
       <c r="E366" t="s">
+        <v>2343</v>
+      </c>
+      <c r="F366" t="s">
+        <v>2344</v>
+      </c>
+      <c r="G366" t="s">
         <v>2345</v>
       </c>
-      <c r="F366" t="s">
+      <c r="H366" t="s">
         <v>2346</v>
-      </c>
-      <c r="G366" t="s">
-        <v>2347</v>
-      </c>
-      <c r="H366" t="s">
-        <v>2348</v>
       </c>
       <c r="I366" t="s">
         <v>984</v>
@@ -19816,25 +19818,25 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
+        <v>2347</v>
+      </c>
+      <c r="B367" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C367" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D367" t="s">
         <v>2349</v>
       </c>
-      <c r="B367" t="s">
+      <c r="E367" t="s">
         <v>2350</v>
       </c>
-      <c r="C367" t="s">
-        <v>1677</v>
-      </c>
-      <c r="D367" t="s">
+      <c r="F367" t="s">
         <v>2351</v>
       </c>
-      <c r="E367" t="s">
+      <c r="G367" t="s">
         <v>2352</v>
-      </c>
-      <c r="F367" t="s">
-        <v>2353</v>
-      </c>
-      <c r="G367" t="s">
-        <v>2354</v>
       </c>
       <c r="H367" t="s">
         <v>76</v>
@@ -19848,28 +19850,28 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B368" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C368" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D368" t="s">
         <v>2355</v>
       </c>
-      <c r="B368" t="s">
+      <c r="E368" t="s">
         <v>2356</v>
       </c>
-      <c r="C368" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D368" t="s">
+      <c r="F368" t="s">
         <v>2357</v>
       </c>
-      <c r="E368" t="s">
+      <c r="G368" t="s">
         <v>2358</v>
       </c>
-      <c r="F368" t="s">
-        <v>2359</v>
-      </c>
-      <c r="G368" t="s">
-        <v>2360</v>
-      </c>
       <c r="H368" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="I368" t="s">
         <v>218</v>
@@ -19880,28 +19882,28 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="B369" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="C369" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="D369" t="s">
         <v>106</v>
       </c>
       <c r="E369" t="s">
+        <v>2361</v>
+      </c>
+      <c r="F369" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G369" t="s">
         <v>2363</v>
       </c>
-      <c r="F369" t="s">
-        <v>2364</v>
-      </c>
-      <c r="G369" t="s">
-        <v>2365</v>
-      </c>
       <c r="H369" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="I369" t="s">
         <v>888</v>
@@ -19912,25 +19914,25 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="B370" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="C370" t="s">
         <v>676</v>
       </c>
       <c r="D370" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E370" t="s">
+        <v>2367</v>
+      </c>
+      <c r="F370" t="s">
         <v>2368</v>
       </c>
-      <c r="E370" t="s">
+      <c r="G370" t="s">
         <v>2369</v>
-      </c>
-      <c r="F370" t="s">
-        <v>2370</v>
-      </c>
-      <c r="G370" t="s">
-        <v>2371</v>
       </c>
       <c r="H370" t="s">
         <v>805</v>
@@ -19944,25 +19946,25 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="B371" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="C371" t="s">
         <v>97</v>
       </c>
       <c r="D371" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="E371" t="s">
+        <v>2372</v>
+      </c>
+      <c r="F371" t="s">
+        <v>2373</v>
+      </c>
+      <c r="G371" t="s">
         <v>2374</v>
-      </c>
-      <c r="F371" t="s">
-        <v>2375</v>
-      </c>
-      <c r="G371" t="s">
-        <v>2376</v>
       </c>
       <c r="H371" t="s">
         <v>1006</v>
@@ -19976,10 +19978,10 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="B372" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="C372" t="s">
         <v>11</v>
@@ -19988,13 +19990,13 @@
         <v>519</v>
       </c>
       <c r="E372" t="s">
+        <v>2377</v>
+      </c>
+      <c r="F372" t="s">
+        <v>2378</v>
+      </c>
+      <c r="G372" t="s">
         <v>2379</v>
-      </c>
-      <c r="F372" t="s">
-        <v>2380</v>
-      </c>
-      <c r="G372" t="s">
-        <v>2381</v>
       </c>
       <c r="H372" t="s">
         <v>76</v>
@@ -20008,28 +20010,28 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B373" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C373" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D373" t="s">
         <v>2382</v>
       </c>
-      <c r="B373" t="s">
+      <c r="E373" t="s">
         <v>2383</v>
       </c>
-      <c r="C373" t="s">
-        <v>1719</v>
-      </c>
-      <c r="D373" t="s">
+      <c r="F373" t="s">
         <v>2384</v>
       </c>
-      <c r="E373" t="s">
+      <c r="G373" t="s">
         <v>2385</v>
       </c>
-      <c r="F373" t="s">
-        <v>2386</v>
-      </c>
-      <c r="G373" t="s">
-        <v>2387</v>
-      </c>
       <c r="H373" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="I373" t="s">
         <v>700</v>
@@ -20040,10 +20042,10 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="B374" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="C374" t="s">
         <v>178</v>
@@ -20052,13 +20054,13 @@
         <v>526</v>
       </c>
       <c r="E374" t="s">
+        <v>2388</v>
+      </c>
+      <c r="F374" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G374" t="s">
         <v>2390</v>
-      </c>
-      <c r="F374" t="s">
-        <v>2391</v>
-      </c>
-      <c r="G374" t="s">
-        <v>2392</v>
       </c>
       <c r="H374" t="s">
         <v>843</v>
@@ -20072,28 +20074,28 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="B375" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="C375" t="s">
         <v>29</v>
       </c>
       <c r="D375" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="E375" t="s">
+        <v>2393</v>
+      </c>
+      <c r="F375" t="s">
+        <v>2394</v>
+      </c>
+      <c r="G375" t="s">
         <v>2395</v>
       </c>
-      <c r="F375" t="s">
+      <c r="H375" t="s">
         <v>2396</v>
-      </c>
-      <c r="G375" t="s">
-        <v>2397</v>
-      </c>
-      <c r="H375" t="s">
-        <v>2398</v>
       </c>
       <c r="I375" t="s">
         <v>94</v>
@@ -20104,10 +20106,10 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="B376" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="C376" t="s">
         <v>309</v>
@@ -20116,13 +20118,13 @@
         <v>65</v>
       </c>
       <c r="E376" t="s">
+        <v>2399</v>
+      </c>
+      <c r="F376" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G376" t="s">
         <v>2401</v>
-      </c>
-      <c r="F376" t="s">
-        <v>2402</v>
-      </c>
-      <c r="G376" t="s">
-        <v>2403</v>
       </c>
       <c r="H376" t="s">
         <v>399</v>
@@ -20136,10 +20138,10 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="B377" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="C377" t="s">
         <v>178</v>
@@ -20148,13 +20150,13 @@
         <v>526</v>
       </c>
       <c r="E377" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F377" t="s">
+        <v>2405</v>
+      </c>
+      <c r="G377" t="s">
         <v>2406</v>
-      </c>
-      <c r="F377" t="s">
-        <v>2407</v>
-      </c>
-      <c r="G377" t="s">
-        <v>2408</v>
       </c>
       <c r="H377" t="s">
         <v>805</v>
@@ -20168,10 +20170,10 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B378" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="C378" t="s">
         <v>782</v>
@@ -20180,13 +20182,13 @@
         <v>72</v>
       </c>
       <c r="E378" t="s">
+        <v>2409</v>
+      </c>
+      <c r="F378" t="s">
+        <v>2410</v>
+      </c>
+      <c r="G378" t="s">
         <v>2411</v>
-      </c>
-      <c r="F378" t="s">
-        <v>2412</v>
-      </c>
-      <c r="G378" t="s">
-        <v>2413</v>
       </c>
       <c r="H378" t="s">
         <v>93</v>
@@ -20200,10 +20202,10 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="B379" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="C379" t="s">
         <v>178</v>
@@ -20212,13 +20214,13 @@
         <v>455</v>
       </c>
       <c r="E379" t="s">
+        <v>2414</v>
+      </c>
+      <c r="F379" t="s">
+        <v>2415</v>
+      </c>
+      <c r="G379" t="s">
         <v>2416</v>
-      </c>
-      <c r="F379" t="s">
-        <v>2417</v>
-      </c>
-      <c r="G379" t="s">
-        <v>2418</v>
       </c>
       <c r="H379" t="s">
         <v>508</v>
@@ -20232,10 +20234,10 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="B380" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="C380" t="s">
         <v>97</v>
@@ -20244,13 +20246,13 @@
         <v>65</v>
       </c>
       <c r="E380" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="F380" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="G380" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="H380" t="s">
         <v>843</v>
@@ -20264,25 +20266,25 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B381" t="s">
+        <v>2422</v>
+      </c>
+      <c r="C381" t="s">
         <v>2423</v>
-      </c>
-      <c r="B381" t="s">
-        <v>2424</v>
-      </c>
-      <c r="C381" t="s">
-        <v>2425</v>
       </c>
       <c r="D381" t="s">
         <v>362</v>
       </c>
       <c r="E381" t="s">
+        <v>2424</v>
+      </c>
+      <c r="F381" t="s">
+        <v>2425</v>
+      </c>
+      <c r="G381" t="s">
         <v>2426</v>
-      </c>
-      <c r="F381" t="s">
-        <v>2427</v>
-      </c>
-      <c r="G381" t="s">
-        <v>2428</v>
       </c>
       <c r="H381" t="s">
         <v>899</v>
@@ -20299,28 +20301,28 @@
         <v>197512</v>
       </c>
       <c r="B382" t="s">
+        <v>2427</v>
+      </c>
+      <c r="C382" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D382" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E382" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F382" t="s">
         <v>2429</v>
       </c>
-      <c r="C382" t="s">
-        <v>2216</v>
-      </c>
-      <c r="D382" t="s">
-        <v>2008</v>
-      </c>
-      <c r="E382" t="s">
+      <c r="G382" t="s">
         <v>2430</v>
       </c>
-      <c r="F382" t="s">
-        <v>2431</v>
-      </c>
-      <c r="G382" t="s">
-        <v>2432</v>
-      </c>
       <c r="H382" s="2" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="I382" s="1" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="J382">
         <v>15000</v>
@@ -20328,10 +20330,10 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="B383" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="C383" t="s">
         <v>11</v>
@@ -20340,16 +20342,16 @@
         <v>12</v>
       </c>
       <c r="E383" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F383" t="s">
+        <v>2434</v>
+      </c>
+      <c r="G383" t="s">
         <v>2435</v>
       </c>
-      <c r="F383" t="s">
-        <v>2436</v>
-      </c>
-      <c r="G383" t="s">
-        <v>2437</v>
-      </c>
       <c r="H383" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="I383" t="s">
         <v>150</v>
@@ -20360,25 +20362,25 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B384" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C384" t="s">
         <v>2438</v>
-      </c>
-      <c r="B384" t="s">
-        <v>2439</v>
-      </c>
-      <c r="C384" t="s">
-        <v>2440</v>
       </c>
       <c r="D384" t="s">
         <v>432</v>
       </c>
       <c r="E384" t="s">
+        <v>2439</v>
+      </c>
+      <c r="F384" t="s">
+        <v>2440</v>
+      </c>
+      <c r="G384" t="s">
         <v>2441</v>
-      </c>
-      <c r="F384" t="s">
-        <v>2442</v>
-      </c>
-      <c r="G384" t="s">
-        <v>2443</v>
       </c>
       <c r="H384" t="s">
         <v>694</v>
@@ -20392,10 +20394,10 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="B385" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="C385" t="s">
         <v>11</v>
@@ -20404,16 +20406,16 @@
         <v>106</v>
       </c>
       <c r="E385" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F385" t="s">
+        <v>2445</v>
+      </c>
+      <c r="G385" t="s">
         <v>2446</v>
       </c>
-      <c r="F385" t="s">
-        <v>2447</v>
-      </c>
-      <c r="G385" t="s">
-        <v>2448</v>
-      </c>
       <c r="H385" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="I385" t="s">
         <v>836</v>
@@ -20424,10 +20426,10 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="B386" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="C386" t="s">
         <v>29</v>
@@ -20436,16 +20438,16 @@
         <v>748</v>
       </c>
       <c r="E386" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F386" t="s">
+        <v>2450</v>
+      </c>
+      <c r="G386" t="s">
         <v>2451</v>
       </c>
-      <c r="F386" t="s">
+      <c r="H386" t="s">
         <v>2452</v>
-      </c>
-      <c r="G386" t="s">
-        <v>2453</v>
-      </c>
-      <c r="H386" t="s">
-        <v>2454</v>
       </c>
       <c r="I386" t="s">
         <v>451</v>
@@ -20456,28 +20458,28 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B387" t="s">
+        <v>2454</v>
+      </c>
+      <c r="C387" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D387" t="s">
         <v>2455</v>
       </c>
-      <c r="B387" t="s">
+      <c r="E387" t="s">
         <v>2456</v>
       </c>
-      <c r="C387" t="s">
-        <v>1766</v>
-      </c>
-      <c r="D387" t="s">
+      <c r="F387" t="s">
         <v>2457</v>
       </c>
-      <c r="E387" t="s">
+      <c r="G387" t="s">
         <v>2458</v>
       </c>
-      <c r="F387" t="s">
-        <v>2459</v>
-      </c>
-      <c r="G387" t="s">
-        <v>2460</v>
-      </c>
       <c r="H387" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="I387" t="s">
         <v>157</v>
@@ -20488,10 +20490,10 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="B388" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="C388" t="s">
         <v>1040</v>
@@ -20500,16 +20502,16 @@
         <v>106</v>
       </c>
       <c r="E388" t="s">
+        <v>2461</v>
+      </c>
+      <c r="F388" t="s">
+        <v>2462</v>
+      </c>
+      <c r="G388" t="s">
         <v>2463</v>
       </c>
-      <c r="F388" t="s">
-        <v>2464</v>
-      </c>
-      <c r="G388" t="s">
-        <v>2465</v>
-      </c>
       <c r="H388" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="I388" t="s">
         <v>530</v>
@@ -20520,10 +20522,10 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="B389" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="C389" t="s">
         <v>736</v>
@@ -20532,16 +20534,16 @@
         <v>1107</v>
       </c>
       <c r="E389" t="s">
+        <v>2466</v>
+      </c>
+      <c r="F389" t="s">
+        <v>2467</v>
+      </c>
+      <c r="G389" t="s">
         <v>2468</v>
       </c>
-      <c r="F389" t="s">
-        <v>2469</v>
-      </c>
-      <c r="G389" t="s">
-        <v>2470</v>
-      </c>
       <c r="H389" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I389" t="s">
         <v>836</v>
@@ -20552,10 +20554,10 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="B390" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="C390" t="s">
         <v>996</v>
@@ -20564,13 +20566,13 @@
         <v>160</v>
       </c>
       <c r="E390" t="s">
+        <v>2471</v>
+      </c>
+      <c r="F390" t="s">
+        <v>2472</v>
+      </c>
+      <c r="G390" t="s">
         <v>2473</v>
-      </c>
-      <c r="F390" t="s">
-        <v>2474</v>
-      </c>
-      <c r="G390" t="s">
-        <v>2475</v>
       </c>
       <c r="H390" t="s">
         <v>1043</v>
@@ -20584,28 +20586,28 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="B391" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="C391" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="D391" t="s">
         <v>65</v>
       </c>
       <c r="E391" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F391" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G391" t="s">
         <v>2478</v>
       </c>
-      <c r="F391" t="s">
-        <v>2479</v>
-      </c>
-      <c r="G391" t="s">
-        <v>2480</v>
-      </c>
       <c r="H391" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="I391" t="s">
         <v>94</v>
@@ -20616,31 +20618,31 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="B392" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="C392" t="s">
         <v>11</v>
       </c>
       <c r="D392" t="s">
+        <v>2481</v>
+      </c>
+      <c r="E392" t="s">
+        <v>2482</v>
+      </c>
+      <c r="F392" t="s">
         <v>2483</v>
       </c>
-      <c r="E392" t="s">
+      <c r="G392" t="s">
         <v>2484</v>
-      </c>
-      <c r="F392" t="s">
-        <v>2485</v>
-      </c>
-      <c r="G392" t="s">
-        <v>2486</v>
       </c>
       <c r="H392" t="s">
         <v>76</v>
       </c>
       <c r="I392" t="s">
-        <v>2487</v>
+        <v>2485</v>
       </c>
       <c r="J392">
         <v>8000</v>
@@ -20648,25 +20650,25 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="B393" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="C393" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="D393" t="s">
         <v>65</v>
       </c>
       <c r="E393" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F393" t="s">
+        <v>2489</v>
+      </c>
+      <c r="G393" t="s">
         <v>2490</v>
-      </c>
-      <c r="F393" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G393" t="s">
-        <v>2492</v>
       </c>
       <c r="H393" t="s">
         <v>611</v>
@@ -20680,10 +20682,10 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="B394" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="C394" t="s">
         <v>37</v>
@@ -20692,13 +20694,13 @@
         <v>362</v>
       </c>
       <c r="E394" t="s">
+        <v>2493</v>
+      </c>
+      <c r="F394" t="s">
+        <v>2494</v>
+      </c>
+      <c r="G394" t="s">
         <v>2495</v>
-      </c>
-      <c r="F394" t="s">
-        <v>2496</v>
-      </c>
-      <c r="G394" t="s">
-        <v>2497</v>
       </c>
       <c r="H394" t="s">
         <v>925</v>
@@ -20712,10 +20714,10 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="B395" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="C395" t="s">
         <v>676</v>
@@ -20724,13 +20726,13 @@
         <v>748</v>
       </c>
       <c r="E395" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="F395" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G395" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
       <c r="H395" t="s">
         <v>701</v>
@@ -20744,25 +20746,25 @@
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B396" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C396" t="s">
         <v>2501</v>
       </c>
-      <c r="B396" t="s">
+      <c r="D396" t="s">
+        <v>1893</v>
+      </c>
+      <c r="E396" t="s">
         <v>2502</v>
       </c>
-      <c r="C396" t="s">
+      <c r="F396" t="s">
         <v>2503</v>
       </c>
-      <c r="D396" t="s">
-        <v>1895</v>
-      </c>
-      <c r="E396" t="s">
+      <c r="G396" t="s">
         <v>2504</v>
-      </c>
-      <c r="F396" t="s">
-        <v>2505</v>
-      </c>
-      <c r="G396" t="s">
-        <v>2506</v>
       </c>
       <c r="H396" t="s">
         <v>76</v>
@@ -20776,10 +20778,10 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B397" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="C397" t="s">
         <v>29</v>
@@ -20788,13 +20790,13 @@
         <v>748</v>
       </c>
       <c r="E397" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F397" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="G397" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="H397" t="s">
         <v>489</v>
@@ -20808,25 +20810,25 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="B398" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="C398" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="D398" t="s">
         <v>989</v>
       </c>
       <c r="E398" t="s">
+        <v>2511</v>
+      </c>
+      <c r="F398" t="s">
+        <v>2512</v>
+      </c>
+      <c r="G398" t="s">
         <v>2513</v>
-      </c>
-      <c r="F398" t="s">
-        <v>2514</v>
-      </c>
-      <c r="G398" t="s">
-        <v>2515</v>
       </c>
       <c r="H398" t="s">
         <v>925</v>
@@ -20840,10 +20842,10 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="B399" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="C399" t="s">
         <v>756</v>
@@ -20852,13 +20854,13 @@
         <v>72</v>
       </c>
       <c r="E399" t="s">
+        <v>2516</v>
+      </c>
+      <c r="F399" t="s">
+        <v>2517</v>
+      </c>
+      <c r="G399" t="s">
         <v>2518</v>
-      </c>
-      <c r="F399" t="s">
-        <v>2519</v>
-      </c>
-      <c r="G399" t="s">
-        <v>2520</v>
       </c>
       <c r="H399" t="s">
         <v>459</v>
@@ -20872,25 +20874,25 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="B400" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="C400" t="s">
         <v>221</v>
       </c>
       <c r="D400" t="s">
+        <v>2521</v>
+      </c>
+      <c r="E400" t="s">
+        <v>2522</v>
+      </c>
+      <c r="F400" t="s">
         <v>2523</v>
       </c>
-      <c r="E400" t="s">
+      <c r="G400" t="s">
         <v>2524</v>
-      </c>
-      <c r="F400" t="s">
-        <v>2525</v>
-      </c>
-      <c r="G400" t="s">
-        <v>2526</v>
       </c>
       <c r="H400" t="s">
         <v>481</v>
@@ -20904,25 +20906,25 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="B401" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="C401" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="D401" t="s">
         <v>65</v>
       </c>
       <c r="E401" t="s">
+        <v>2527</v>
+      </c>
+      <c r="F401" t="s">
+        <v>2528</v>
+      </c>
+      <c r="G401" t="s">
         <v>2529</v>
-      </c>
-      <c r="F401" t="s">
-        <v>2530</v>
-      </c>
-      <c r="G401" t="s">
-        <v>2531</v>
       </c>
       <c r="H401" t="s">
         <v>142</v>
@@ -20936,10 +20938,10 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="B402" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="C402" t="s">
         <v>190</v>
@@ -20951,13 +20953,13 @@
         <v>340</v>
       </c>
       <c r="F402" t="s">
+        <v>2532</v>
+      </c>
+      <c r="G402" t="s">
+        <v>2533</v>
+      </c>
+      <c r="H402" t="s">
         <v>2534</v>
-      </c>
-      <c r="G402" t="s">
-        <v>2535</v>
-      </c>
-      <c r="H402" t="s">
-        <v>2536</v>
       </c>
       <c r="I402" t="s">
         <v>950</v>
@@ -20968,25 +20970,25 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="B403" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="C403" t="s">
         <v>556</v>
       </c>
       <c r="D403" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E403" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F403" t="s">
         <v>2539</v>
       </c>
-      <c r="E403" t="s">
+      <c r="G403" t="s">
         <v>2540</v>
-      </c>
-      <c r="F403" t="s">
-        <v>2541</v>
-      </c>
-      <c r="G403" t="s">
-        <v>2542</v>
       </c>
       <c r="H403" t="s">
         <v>110</v>
@@ -21000,13 +21002,13 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="B404" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="C404" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="D404" t="s">
         <v>577</v>
@@ -21015,16 +21017,16 @@
         <v>90</v>
       </c>
       <c r="F404" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="G404" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="H404" t="s">
         <v>142</v>
       </c>
       <c r="I404" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="J404">
         <v>10000</v>
@@ -21032,28 +21034,28 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B405" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C405" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D405" t="s">
         <v>2547</v>
       </c>
-      <c r="B405" t="s">
+      <c r="E405" t="s">
         <v>2548</v>
       </c>
-      <c r="C405" t="s">
-        <v>1766</v>
-      </c>
-      <c r="D405" t="s">
+      <c r="F405" t="s">
         <v>2549</v>
       </c>
-      <c r="E405" t="s">
+      <c r="G405" t="s">
         <v>2550</v>
       </c>
-      <c r="F405" t="s">
+      <c r="H405" t="s">
         <v>2551</v>
-      </c>
-      <c r="G405" t="s">
-        <v>2552</v>
-      </c>
-      <c r="H405" t="s">
-        <v>2553</v>
       </c>
       <c r="I405" t="s">
         <v>984</v>
@@ -21064,28 +21066,28 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="B406" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="C406" t="s">
         <v>37</v>
       </c>
       <c r="D406" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="E406" t="s">
+        <v>2554</v>
+      </c>
+      <c r="F406" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G406" t="s">
         <v>2556</v>
       </c>
-      <c r="F406" t="s">
-        <v>2557</v>
-      </c>
-      <c r="G406" t="s">
-        <v>2558</v>
-      </c>
       <c r="H406" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I406" t="s">
         <v>367</v>
@@ -21096,10 +21098,10 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="B407" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="C407" t="s">
         <v>556</v>
@@ -21108,13 +21110,13 @@
         <v>526</v>
       </c>
       <c r="E407" t="s">
+        <v>2559</v>
+      </c>
+      <c r="F407" t="s">
+        <v>2560</v>
+      </c>
+      <c r="G407" t="s">
         <v>2561</v>
-      </c>
-      <c r="F407" t="s">
-        <v>2562</v>
-      </c>
-      <c r="G407" t="s">
-        <v>2563</v>
       </c>
       <c r="H407" t="s">
         <v>587</v>
@@ -21128,10 +21130,10 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="B408" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="C408" t="s">
         <v>268</v>
@@ -21140,13 +21142,13 @@
         <v>106</v>
       </c>
       <c r="E408" t="s">
+        <v>2564</v>
+      </c>
+      <c r="F408" t="s">
+        <v>2565</v>
+      </c>
+      <c r="G408" t="s">
         <v>2566</v>
-      </c>
-      <c r="F408" t="s">
-        <v>2567</v>
-      </c>
-      <c r="G408" t="s">
-        <v>2568</v>
       </c>
       <c r="H408" t="s">
         <v>508</v>
